--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO5" headerRowCount="1">
+  <autoFilter ref="A1:CO5"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$5)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$5)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,1127 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>7a7b4ead9f41446d</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:35:44.644443Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>401886548</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.523162</v>
+      </c>
+      <c r="P2" s="28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q2" s="28" t="n">
+        <v>0.193129</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:51:58.565109Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.63 (home) / 0.95 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (tsc-clbf-gal-ven-2026-07-27-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:34:15.330265Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK2" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>19fc9ad985604d74</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:35:44.644443Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>401886548</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.5234799999999999</v>
+      </c>
+      <c r="P3" s="28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q3" s="28" t="n">
+        <v>-0.116808</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:51:58.610670Z</t>
+        </is>
+      </c>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.63 (home) / 0.95 (away) from EWMA attack/defense strengths. Executable ask 0.6400 (atc-clbf-gal-ven-2026-07-27-gal).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:34:15.326479Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>c75f6d1022da4a63</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:53:46.963522Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T23:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>401843998</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.550664</v>
+      </c>
+      <c r="P4" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="28" t="n">
+        <v>0.180294</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:11.783634Z</t>
+        </is>
+      </c>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3700 (tsc-arg2-atl-alm-2026-07-27-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:46.180696Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK4" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>a46c289941a345c2</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:53:46.963522Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T23:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>401843998</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P5" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q5" s="28" t="n">
+        <v>-0.153176</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:11.829328Z</t>
+        </is>
+      </c>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6100 (atc-arg2-atl-alm-2026-07-27-atl).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:46.097852Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -2516,7 +2516,7 @@
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO5" headerRowCount="1">
-  <autoFilter ref="A1:CO5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO23" headerRowCount="1">
+  <autoFilter ref="A1:CO23"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$23)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$23,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")/(COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"win")+COUNTIFS('Picks'!$BX$2:$BX$23,"&gt;0",'Picks'!$V$2:$V$23,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$23)/SUM('Picks'!$BX$2:$BX$23),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$23)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$23,"&lt;&gt;",'Picks'!$AB$2:$AB$23),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$23,'Picks'!$AM$2:$AM$23,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A14,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A15,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled",'Picks'!$V$2:$V$23,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$23,'Picks'!$H$2:$H$23,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$23,'Picks'!$H$2:$H$23,$A16,'Picks'!$U$2:$U$23,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO5"/>
+  <dimension ref="A1:CO23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2691,6 +2691,4922 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
     </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>5dcf18c1bd674c37</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:34:14.874473Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:30Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>401860254</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P6" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q6" s="28" t="n">
+        <v>-0.103272</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:41:46.905781Z</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-brb-juv-ava-2026-07-28-juv).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:32:26.107744Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>c1a2615685634f23</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:34:14.874473Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:30Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>401860261</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Athletic</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P7" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="28" t="n">
+        <v>0.206199</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:41:46.978948Z</t>
+        </is>
+      </c>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.2500 (atc-brb-pop-ath-2026-07-28-pop).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>Athletic</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Athletic</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Athletic</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:32:26.083099Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>71dc8bd5d8eb498a</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:34:14.874473Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>401841452</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P8" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="28" t="n">
+        <v>-0.043801</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:41:47.313571Z</t>
+        </is>
+      </c>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5000 (atc-lpa-slo-gye-2026-07-28-slo).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:32:27.095637Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>538e4eae98a44836</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:34:14.874473Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>401874071</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P9" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q9" s="28" t="n">
+        <v>0.005749</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:41:49.355103Z</t>
+        </is>
+      </c>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-sud-tig-nac-2026-07-28-tig).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:32:28.187625Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>9d29b7c025c54f14</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:39:16.759753Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:35Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>401860253</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P10" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q10" s="28" t="n">
+        <v>-0.053605</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:41:49.433624Z</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-brb-fec-bot-2026-07-28-fec).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:37:59.431647Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>b4c3bd27b9274dbf</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:39:16.759753Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:15Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>401841453</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P11" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="28" t="n">
+        <v>-0.02457</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:41:49.507236Z</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4800 (atc-lpa-ros-rac-2026-07-28-ros).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T23:38:00.751821Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>5d005d5149204d49</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:55:19.773254Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T10:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>401872736</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.440542</v>
+      </c>
+      <c r="P12" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q12" s="28" t="n">
+        <v>-0.199746</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:04:55.440111Z</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.39 (home) / 1.71 (away) from EWMA attack/defense strengths. Executable ask 0.6400 (atc-clbf-cer-bvb-2026-07-29-bvb).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T08:52:45.504203Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>f8c013a541034830</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:07:40.379188Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:30Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>401841461</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P13" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q13" s="28" t="n">
+        <v>0.046363</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:52.147509Z</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-lpa-bar-ald-2026-07-29-bar).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:06:01.050931Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>2016ad82b8004b89</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:45:15.881226Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:30Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>401841171</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>285</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P14" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q14" s="28" t="n">
+        <v>0.196459</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:52.241515Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.2600 (atc-bra-int-fla-2026-07-29-int).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:43:19.651886Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>285</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>9eab45bc1b49434a</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:45:15.881226Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:30Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>401841170</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P15" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="28" t="n">
+        <v>-0.123633</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:52.337713Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5800 (atc-bra-mir-cre-2026-07-29-mir).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:43:19.742689Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>543936a84904488a</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:45:15.881226Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:30Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>401841177</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P16" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q16" s="28" t="n">
+        <v>-0.114616</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:52.435602Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5700 (atc-bra-flu-bah-2026-07-29-flu).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:43:20.222742Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>e4ff84b7e06b4da7</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:45:15.881226Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T22:15Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>401841457</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>355</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.456199</v>
+      </c>
+      <c r="P17" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q17" s="28" t="n">
+        <v>0.236419</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:52.533511Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.2200 (atc-lpa-gim-riv-2026-07-29-gim).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:43:20.814669Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>355</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>6fe762116e044f29</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:45:15.881226Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T23:30Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>401863532</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.5541700000000001</v>
+      </c>
+      <c r="P18" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q18" s="28" t="n">
+        <v>-0.14553</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T04:12:55.723807Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 2.12 (home) / 1.29 (away) from EWMA attack/defense strengths. Executable ask 0.7000 (atc-clbf-lfc-wre-2026-07-29-lfc).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>0361718a19f38c3d244b71cb6b1f2e7e14a86925e833d2186645250fc084b969</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:43:24.705734Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>71676e5d4e784ed5</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:52:58.895214Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:30Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>401841173</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>257</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.280112</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P19" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q19" s="28" t="n">
+        <v>0.176023</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.2800 (atc-bra-cor-cru-2026-07-30-cor).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:50:44.925185Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>257</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.280112</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>e75a6e2514f84613</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:52:58.895214Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:15Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>401841456</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P20" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="28" t="n">
+        <v>-0.143865</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6000 (atc-lpa-ind-new-2026-07-30-ind).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:50:45.970537Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>15daf019df0f4f36</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:52:58.895214Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:30Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>401874162</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Caracas FC</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>233</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P21" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q21" s="28" t="n">
+        <v>0.155835</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-sud-cfa-isf-2026-07-30-cfa).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Caracas FC</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Caracas FC</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Caracas FC</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:50:47.012263Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>233</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>98ca1acac7d84bd7</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:52:58.895214Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:30Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>401874164</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.396866</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q22" s="28" t="n">
+        <v>-0.112938</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.30 (home) / 1.46 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-sud-ohi-boc-2026-07-30-boc).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:50:47.670613Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>fda9ef34146140ad</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:52:58.895214Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T23:30Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>401897750</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.356905</v>
+      </c>
+      <c r="P23" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q23" s="28" t="n">
+        <v>0.007255</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.19 (home) / 1.15 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-clbf-lee-sun-2026-07-30-sun).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:50:48.716553Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -6295,12 +6295,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>71676e5d4e784ed5</t>
+          <t>93e09b788ab2429d</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:52:58.895214Z</t>
+          <t>2026-07-30T17:19:58.850831Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:44.925185Z</t>
+          <t>2026-07-30T17:17:45.955602Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6558,12 +6558,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>e75a6e2514f84613</t>
+          <t>ee014f77211f42fb</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:52:58.895214Z</t>
+          <t>2026-07-30T17:19:58.850831Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O20" s="28" t="n">
         <v>0.456135</v>
@@ -6623,7 +6623,7 @@
         <v>0.2</v>
       </c>
       <c r="Q20" s="28" t="n">
-        <v>-0.143865</v>
+        <v>-0.15324</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6000 (atc-lpa-ind-new-2026-07-30-ind).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6100 (atc-lpa-ind-new-2026-07-30-ind).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:45.970537Z</t>
+          <t>2026-07-30T17:17:47.022670Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6781,13 +6781,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6821,12 +6821,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>15daf019df0f4f36</t>
+          <t>14ffc20bd50b4b91</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:52:58.895214Z</t>
+          <t>2026-07-30T17:19:58.850831Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -6871,13 +6871,13 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.309598</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.456135</v>
@@ -6886,10 +6886,10 @@
         <v>0.2</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.155835</v>
+        <v>0.146537</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>0</v>
@@ -6915,7 +6915,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-sud-cfa-isf-2026-07-30-cfa).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3100 (atc-sud-cfa-isf-2026-07-30-cfa).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:47.012263Z</t>
+          <t>2026-07-30T17:17:48.185594Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7044,13 +7044,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.309598</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7084,12 +7084,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>98ca1acac7d84bd7</t>
+          <t>4ca0a538fc214ecc</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:52:58.895214Z</t>
+          <t>2026-07-30T17:19:58.850831Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:47.670613Z</t>
+          <t>2026-07-30T17:17:48.653238Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7347,12 +7347,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>fda9ef34146140ad</t>
+          <t>852be6d2565745f7</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:52:58.895214Z</t>
+          <t>2026-07-30T17:19:58.850831Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:50:48.716553Z</t>
+          <t>2026-07-30T17:17:49.572444Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -6295,12 +6295,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>93e09b788ab2429d</t>
+          <t>c10d04e520184502</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:19:58.850831Z</t>
+          <t>2026-07-30T17:37:41.381091Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:45.955602Z</t>
+          <t>2026-07-30T17:35:43.771762Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6558,12 +6558,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>ee014f77211f42fb</t>
+          <t>c9452728cb6d4cac</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:19:58.850831Z</t>
+          <t>2026-07-30T17:37:41.381091Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:47.022670Z</t>
+          <t>2026-07-30T17:35:44.822306Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6821,12 +6821,12 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>14ffc20bd50b4b91</t>
+          <t>20ae350213fb4de6</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:19:58.850831Z</t>
+          <t>2026-07-30T17:37:41.381091Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:48.185594Z</t>
+          <t>2026-07-30T17:35:45.885777Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7084,12 +7084,12 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>4ca0a538fc214ecc</t>
+          <t>d6bec6389dd2414b</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:19:58.850831Z</t>
+          <t>2026-07-30T17:37:41.381091Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -7134,13 +7134,13 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.396866</v>
@@ -7149,7 +7149,7 @@
         <v>0.19</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>-0.112938</v>
+        <v>-0.122365</v>
       </c>
       <c r="R22" s="26" t="n">
         <v>0</v>
@@ -7178,7 +7178,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.30 (home) / 1.46 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-sud-ohi-boc-2026-07-30-boc).</t>
+          <t>Poisson-DC rates 1.30 (home) / 1.46 (away) from EWMA attack/defense strengths. Executable ask 0.5200 (atc-sud-ohi-boc-2026-07-30-boc).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:48.653238Z</t>
+          <t>2026-07-30T17:35:46.319207Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7307,13 +7307,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.925926</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.519231</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7347,12 +7347,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>852be6d2565745f7</t>
+          <t>d63326cb28cf4f1b</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:19:58.850831Z</t>
+          <t>2026-07-30T17:37:41.381091Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:17:49.572444Z</t>
+          <t>2026-07-30T17:35:47.233189Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO67" headerRowCount="1">
-  <autoFilter ref="A1:CO67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO82" headerRowCount="1">
+  <autoFilter ref="A1:CO82"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$67)</f>
+        <f>COUNTA('Picks'!$A$2:$A$82)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$82,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$82,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")+COUNTIFS('Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$67,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$82,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")/(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"win")/(COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"win")+COUNTIFS('Picks'!$BX$2:$BX$82,"&gt;0",'Picks'!$V$2:$V$82,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$67)/SUM('Picks'!$BX$2:$BX$67),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$82)/SUM('Picks'!$BX$2:$BX$82),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$67)</f>
+        <f>SUM('Picks'!$BY$2:$BY$82)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$67,"&lt;&gt;",'Picks'!$AB$2:$AB$67),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$82,"&lt;&gt;",'Picks'!$AB$2:$AB$82),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$82,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$82,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$67,'Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$82,'Picks'!$AM$2:$AM$82,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$82,'Picks'!$H$2:$H$82,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$82,'Picks'!$H$2:$H$82,$A14,'Picks'!$U$2:$U$82,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$82,'Picks'!$H$2:$H$82,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$82,'Picks'!$H$2:$H$82,$A15,'Picks'!$U$2:$U$82,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled",'Picks'!$V$2:$V$82,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$82,'Picks'!$H$2:$H$82,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$82,'Picks'!$H$2:$H$82,$A16,'Picks'!$U$2:$U$82,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO67"/>
+  <dimension ref="A1:CO82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11084,18 +11084,32 @@
       </c>
       <c r="U36" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y36" s="25" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
+      <c r="AC36" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:10.166427Z</t>
+        </is>
+      </c>
       <c r="AE36" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.53 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.2900 (atc-pdc-eve-col-2026-08-01-eve).</t>
@@ -11108,7 +11122,7 @@
       </c>
       <c r="AG36" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH36" s="24" t="n"/>
@@ -11626,18 +11640,32 @@
       </c>
       <c r="U38" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W38" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X38" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y38" s="25" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
+      <c r="AC38" s="30" t="n">
+        <v>1.6827</v>
+      </c>
+      <c r="AD38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:14.226095Z</t>
+        </is>
+      </c>
       <c r="AE38" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.27 (home) / 2.09 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (tsc-mls-dcu-nas-2026-08-01-2pt5).</t>
@@ -11893,18 +11921,32 @@
       </c>
       <c r="U39" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W39" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y39" s="25" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
+      <c r="AC39" s="30" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="AD39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:26:21.106575Z</t>
+        </is>
+      </c>
       <c r="AE39" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 2.60 (home) / 2.52 (away) from EWMA attack/defense strengths. Executable ask 0.7600 (tsc-mls-fcc-sje-2026-08-01-2pt5).</t>
@@ -12160,18 +12202,32 @@
       </c>
       <c r="U40" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W40" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X40" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y40" s="25" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
+      <c r="AC40" s="30" t="n">
+        <v>0.7018</v>
+      </c>
+      <c r="AD40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:14.497023Z</t>
+        </is>
+      </c>
       <c r="AE40" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 3.37 (home) / 1.57 (away) from EWMA attack/defense strengths. Executable ask 0.7400 (tsc-mls-mia-clb-2026-08-01-2pt5).</t>
@@ -12427,18 +12483,32 @@
       </c>
       <c r="U41" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X41" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y41" s="25" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
+      <c r="AC41" s="30" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="AD41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:14.740324Z</t>
+        </is>
+      </c>
       <c r="AE41" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.93 (home) / 1.08 (away) from EWMA attack/defense strengths. Executable ask 0.6200 (tsc-mls-phi-atl-2026-08-01-2pt5).</t>
@@ -12692,18 +12762,32 @@
       </c>
       <c r="U42" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X42" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y42" s="25" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
+      <c r="AC42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:15.055587Z</t>
+        </is>
+      </c>
       <c r="AE42" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.27 (home) / 2.09 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-mls-dcu-nas-2026-08-01-nas).</t>
@@ -12955,18 +13039,32 @@
       </c>
       <c r="U43" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y43" s="25" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
+      <c r="AC43" s="30" t="n">
+        <v>1.1574</v>
+      </c>
+      <c r="AD43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:26:21.397669Z</t>
+        </is>
+      </c>
       <c r="AE43" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 2.60 (home) / 2.52 (away) from EWMA attack/defense strengths. Executable ask 0.5200 (atc-mls-fcc-sje-2026-08-01-fcc).</t>
@@ -13218,18 +13316,32 @@
       </c>
       <c r="U44" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y44" s="25" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
+      <c r="AC44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:15.417178Z</t>
+        </is>
+      </c>
       <c r="AE44" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 3.37 (home) / 1.57 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-mls-mia-clb-2026-08-01-mia).</t>
@@ -13481,18 +13593,32 @@
       </c>
       <c r="U45" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y45" s="25" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
+      <c r="AC45" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:15.763444Z</t>
+        </is>
+      </c>
       <c r="AE45" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.93 (home) / 1.08 (away) from EWMA attack/defense strengths. Executable ask 0.6100 (atc-mls-phi-atl-2026-08-01-phi).</t>
@@ -13744,18 +13870,32 @@
       </c>
       <c r="U46" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y46" s="25" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
+      <c r="AC46" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:10.459392Z</t>
+        </is>
+      </c>
       <c r="AE46" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.59 (home) / 1.20 (away) from EWMA attack/defense strengths. Executable ask 0.5900 (atc-lpa-est-def-2026-08-01-est).</t>
@@ -14007,18 +14147,32 @@
       </c>
       <c r="U47" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X47" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y47" s="25" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
+      <c r="AC47" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:17.235577Z</t>
+        </is>
+      </c>
       <c r="AE47" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.72 (home) / 1.20 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-lpa-rac-tig-2026-08-01-rac).</t>
@@ -14031,7 +14185,7 @@
       </c>
       <c r="AG47" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH47" s="24" t="n"/>
@@ -14270,18 +14424,32 @@
       </c>
       <c r="U48" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y48" s="25" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
+      <c r="AC48" s="30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:10.837881Z</t>
+        </is>
+      </c>
       <c r="AE48" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.72 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-pdc-pal-coq-2026-08-01-pal).</t>
@@ -14453,22 +14621,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>810dacf83ae54176</t>
+          <t>d5a1a0d79fb04e60</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:31:04.263242Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T01:00Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>401877966</t>
+          <t>761704</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14478,76 +14646,92 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-317</v>
+        <v>-223</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.44843</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.690402</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.676403</v>
       </c>
       <c r="P49" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q49" s="28" t="n">
-        <v>-0.304057</v>
+        <v>-0.013999</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S49" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W49" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U49" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
+      <c r="X49" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y49" s="25" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
+      <c r="AC49" s="30" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="AD49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:17.505871Z</t>
+        </is>
+      </c>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.7600 (atc-lco-san-onc-2026-08-02-san).</t>
+          <t>Poisson-DC rates 2.21 (home) / 1.28 (away) from EWMA attack/defense strengths. Executable ask 0.6900 (tsc-mls-chi-clt-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14588,32 +14772,32 @@
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14666,7 +14850,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:28:06.703532Z</t>
+          <t>2026-08-01T23:52:03.726485Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14674,15 +14858,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ49" s="25" t="n"/>
+      <c r="BJ49" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK49" s="26" t="n">
-        <v>-317</v>
+        <v>-223</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.315457</v>
+        <v>1.44843</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.760192</v>
+        <v>0.690402</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -14716,22 +14902,22 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>59a5cbb0c8ed4adc</t>
+          <t>77cbdb972f24408c</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:30Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>401841470</t>
+          <t>761703</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -14741,76 +14927,92 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K50" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>233</v>
+        <v>-170</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>3.33</v>
+        <v>1.588235</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.62963</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.66611</v>
       </c>
       <c r="P50" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>0.155835</v>
+        <v>0.03648</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="S50" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W50" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U50" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
+      <c r="X50" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y50" s="25" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
+      <c r="AC50" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:17.790482Z</t>
+        </is>
+      </c>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-lpa-ald-gim-2026-08-02-ald).</t>
+          <t>Poisson-DC rates 1.78 (home) / 1.65 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (tsc-mls-min-sdg-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -14820,7 +15022,7 @@
       </c>
       <c r="AG50" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH50" s="24" t="n"/>
@@ -14851,32 +15053,32 @@
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -14929,7 +15131,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:24.896824Z</t>
+          <t>2026-08-01T23:52:06.222075Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -14937,15 +15139,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ50" s="25" t="n"/>
+      <c r="BJ50" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK50" s="26" t="n">
-        <v>233</v>
+        <v>-170</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>3.33</v>
+        <v>1.588235</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.62963</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -14979,22 +15183,22 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>cbd273cc3aef4940</t>
+          <t>6fd0a3d28ba44e1a</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:00Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>401841473</t>
+          <t>761706</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -15004,53 +15208,55 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>300</v>
+        <v>-144</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>4</v>
+        <v>1.694444</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.25</v>
+        <v>0.590164</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.398039</v>
+        <v>0.651724</v>
       </c>
       <c r="P51" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q51" s="28" t="n">
-        <v>0.148039</v>
+        <v>0.06156</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15059,21 +15265,35 @@
       </c>
       <c r="U51" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X51" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y51" s="25" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
+      <c r="AC51" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:18.086130Z</t>
+        </is>
+      </c>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2500 (atc-lpa-new-boc-2026-08-02-new).</t>
+          <t>Poisson-DC rates 1.49 (home) / 1.87 (away) from EWMA attack/defense strengths. Executable ask 0.5900 (tsc-mls-skc-hou-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15083,7 +15303,7 @@
       </c>
       <c r="AG51" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH51" s="24" t="n"/>
@@ -15114,32 +15334,32 @@
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15192,7 +15412,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:24.896136Z</t>
+          <t>2026-08-01T23:52:07.836349Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15200,15 +15420,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ51" s="25" t="n"/>
+      <c r="BJ51" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK51" s="26" t="n">
-        <v>300</v>
+        <v>-144</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>4</v>
+        <v>1.694444</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.25</v>
+        <v>0.590164</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15242,22 +15464,22 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>fe06727d3c8b414f</t>
+          <t>90c023aa72c64cfc</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T22:15Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>401841476</t>
+          <t>761705</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -15267,76 +15489,92 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I52" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K52" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>113</v>
+        <v>-178</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>2.13</v>
+        <v>1.561798</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.640288</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.623765</v>
       </c>
       <c r="P52" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>0.066432</v>
+        <v>-0.016523</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S52" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
+      <c r="X52" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y52" s="25" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
+      <c r="AC52" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:18.397668Z</t>
+        </is>
+      </c>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-lpa-riv-ros-2026-08-02-riv).</t>
+          <t>Poisson-DC rates 1.71 (home) / 1.51 (away) from EWMA attack/defense strengths. Executable ask 0.6400 (tsc-mls-stl-rsl-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -15346,7 +15584,7 @@
       </c>
       <c r="AG52" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH52" s="24" t="n"/>
@@ -15377,32 +15615,32 @@
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -15455,7 +15693,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:25.343861Z</t>
+          <t>2026-08-01T23:52:08.422932Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15463,15 +15701,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ52" s="25" t="n"/>
+      <c r="BJ52" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK52" s="26" t="n">
-        <v>113</v>
+        <v>-178</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>2.13</v>
+        <v>1.561798</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.640288</v>
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>
@@ -15505,22 +15745,22 @@
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>2e6e431825db47ab</t>
+          <t>0d3ad5512fa74cd7</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T01:30Z</t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>401844015</t>
+          <t>761707</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -15530,76 +15770,92 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I53" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K53" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-104</v>
+        <v>-138</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.724638</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.579832</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.683176</v>
       </c>
       <c r="P53" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q53" s="28" t="n">
-        <v>-0.053669</v>
+        <v>0.103344</v>
       </c>
       <c r="R53" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W53" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="29" t="n">
+      <c r="X53" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
       <c r="Y53" s="25" t="n"/>
       <c r="Z53" s="26" t="n"/>
       <c r="AA53" s="28" t="n"/>
       <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
-      <c r="AD53" s="24" t="n"/>
+      <c r="AC53" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:26:21.660283Z</t>
+        </is>
+      </c>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-arg2-cjh-caa-2026-08-01-cjh).</t>
+          <t>Poisson-DC rates 2.28 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5800 (tsc-mls-col-aus-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -15609,7 +15865,7 @@
       </c>
       <c r="AG53" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH53" s="24" t="n"/>
@@ -15640,32 +15896,32 @@
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -15718,7 +15974,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:25.941968Z</t>
+          <t>2026-08-01T23:52:11.070621Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -15726,15 +15982,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ53" s="25" t="n"/>
+      <c r="BJ53" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK53" s="26" t="n">
-        <v>-104</v>
+        <v>-138</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.724638</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.579832</v>
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
@@ -15768,22 +16026,22 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>45e1beeb6e42443f</t>
+          <t>bc1b966bcbff4244</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T02:30Z</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>401844019</t>
+          <t>761709</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
@@ -15793,76 +16051,92 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G54" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I54" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K54" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L54" s="26" t="n">
-        <v>-1567</v>
+        <v>-178</v>
       </c>
       <c r="M54" s="27" t="n">
-        <v>1.063816</v>
+        <v>1.561798</v>
       </c>
       <c r="N54" s="28" t="n">
-        <v>0.940012</v>
+        <v>0.640288</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.6876370000000001</v>
       </c>
       <c r="P54" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q54" s="28" t="n">
-        <v>-0.483877</v>
+        <v>0.047349</v>
       </c>
       <c r="R54" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W54" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U54" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V54" s="24" t="n"/>
-      <c r="W54" s="26" t="n"/>
-      <c r="X54" s="26" t="n"/>
+      <c r="X54" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y54" s="25" t="n"/>
       <c r="Z54" s="26" t="n"/>
       <c r="AA54" s="28" t="n"/>
       <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n"/>
-      <c r="AD54" s="24" t="n"/>
+      <c r="AC54" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T05:39:24.511943Z</t>
+        </is>
+      </c>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.9400 (atc-arg2-ste-casm-2026-08-02-ste).</t>
+          <t>Poisson-DC rates 1.76 (home) / 1.79 (away) from EWMA attack/defense strengths. Executable ask 0.6400 (tsc-mls-lag-dal-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -15872,7 +16146,7 @@
       </c>
       <c r="AG54" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH54" s="24" t="n"/>
@@ -15903,32 +16177,32 @@
       </c>
       <c r="AP54" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="AQ54" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="AR54" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="AS54" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="AT54" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="AU54" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="AV54" s="24" t="n"/>
@@ -15981,7 +16255,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:26.298294Z</t>
+          <t>2026-08-01T23:52:12.107324Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -15989,15 +16263,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ54" s="25" t="n"/>
+      <c r="BJ54" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK54" s="26" t="n">
-        <v>-1567</v>
+        <v>-178</v>
       </c>
       <c r="BL54" s="27" t="n">
-        <v>1.063816</v>
+        <v>1.561798</v>
       </c>
       <c r="BM54" s="28" t="n">
-        <v>0.940012</v>
+        <v>0.640288</v>
       </c>
       <c r="BN54" s="28" t="n"/>
       <c r="BO54" s="28" t="n"/>
@@ -16031,22 +16307,22 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>fcca556c7f944353</t>
+          <t>22fbb5383a354f59</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:30Z</t>
+          <t>2026-08-02T02:45Z</t>
         </is>
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>401844012</t>
+          <t>761708</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -16056,76 +16332,92 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="G55" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I55" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J55" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J55" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>-150</v>
+        <v>-203</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.492611</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.6</v>
+        <v>0.669967</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.666723</v>
       </c>
       <c r="P55" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q55" s="28" t="n">
-        <v>-0.143865</v>
+        <v>-0.003244</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S55" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U55" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V55" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W55" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T55" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U55" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V55" s="24" t="n"/>
-      <c r="W55" s="26" t="n"/>
-      <c r="X55" s="26" t="n"/>
+      <c r="X55" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y55" s="25" t="n"/>
       <c r="Z55" s="26" t="n"/>
       <c r="AA55" s="28" t="n"/>
       <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="30" t="n"/>
-      <c r="AD55" s="24" t="n"/>
+      <c r="AC55" s="30" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="AD55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T05:39:25.044697Z</t>
+        </is>
+      </c>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6000 (atc-arg2-cat-gyt-2026-08-02-cat).</t>
+          <t>Poisson-DC rates 1.85 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.6700 (tsc-mls-por-sea-2026-08-01-2pt5).</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -16166,32 +16458,32 @@
       </c>
       <c r="AP55" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="AQ55" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="AR55" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="AS55" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="AT55" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="AU55" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="AV55" s="24" t="n"/>
@@ -16244,7 +16536,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:26.405115Z</t>
+          <t>2026-08-01T23:52:13.426637Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -16252,15 +16544,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ55" s="25" t="n"/>
+      <c r="BJ55" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK55" s="26" t="n">
-        <v>-150</v>
+        <v>-203</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.492611</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.6</v>
+        <v>0.669967</v>
       </c>
       <c r="BN55" s="28" t="n"/>
       <c r="BO55" s="28" t="n"/>
@@ -16294,22 +16588,22 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>db63c10389164e6f</t>
+          <t>fc4e7c8832354064</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:00Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>401844026</t>
+          <t>761704</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -16319,12 +16613,12 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
@@ -16344,51 +16638,65 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-117</v>
+        <v>-186</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.537634</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.65035</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.576863</v>
       </c>
       <c r="P56" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q56" s="28" t="n">
-        <v>-0.083036</v>
+        <v>-0.073487</v>
       </c>
       <c r="R56" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S56" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U56" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V56" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W56" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T56" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U56" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V56" s="24" t="n"/>
-      <c r="W56" s="26" t="n"/>
-      <c r="X56" s="26" t="n"/>
+      <c r="X56" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y56" s="25" t="n"/>
       <c r="Z56" s="26" t="n"/>
       <c r="AA56" s="28" t="n"/>
       <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="30" t="n"/>
-      <c r="AD56" s="24" t="n"/>
+      <c r="AC56" s="30" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AD56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:18.789170Z</t>
+        </is>
+      </c>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5400 (atc-arg2-dma-abo-2026-08-02-dma).</t>
+          <t>Poisson-DC rates 2.21 (home) / 1.28 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-mls-chi-clt-2026-08-01-chi).</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -16429,32 +16737,32 @@
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Charlotte FC</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Fire FC</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -16507,7 +16815,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:26.833829Z</t>
+          <t>2026-08-01T23:52:03.002096Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -16517,13 +16825,13 @@
       </c>
       <c r="BJ56" s="25" t="n"/>
       <c r="BK56" s="26" t="n">
-        <v>-117</v>
+        <v>-186</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.537634</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.65035</v>
       </c>
       <c r="BN56" s="28" t="n"/>
       <c r="BO56" s="28" t="n"/>
@@ -16557,22 +16865,22 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>1bef6a778fd041d0</t>
+          <t>0c98127e634e4762</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:30Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>401844014</t>
+          <t>761703</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
@@ -16582,12 +16890,12 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">
@@ -16607,51 +16915,65 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-1567</v>
+        <v>104</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.063816</v>
+        <v>2.04</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.940012</v>
+        <v>0.490196</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.405166</v>
       </c>
       <c r="P57" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>-0.483877</v>
+        <v>-0.08502999999999999</v>
       </c>
       <c r="R57" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S57" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V57" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W57" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T57" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U57" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V57" s="24" t="n"/>
-      <c r="W57" s="26" t="n"/>
-      <c r="X57" s="26" t="n"/>
+      <c r="X57" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y57" s="25" t="n"/>
       <c r="Z57" s="26" t="n"/>
       <c r="AA57" s="28" t="n"/>
       <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="30" t="n"/>
-      <c r="AD57" s="24" t="n"/>
+      <c r="AC57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:19.306168Z</t>
+        </is>
+      </c>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.9400 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
+          <t>Poisson-DC rates 1.78 (home) / 1.65 (away) from EWMA attack/defense strengths. Executable ask 0.4900 (atc-mls-min-sdg-2026-08-01-min).</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -16692,32 +17014,32 @@
       </c>
       <c r="AP57" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="AQ57" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="AR57" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="AS57" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="AT57" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="AU57" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United FC</t>
         </is>
       </c>
       <c r="AV57" s="24" t="n"/>
@@ -16770,7 +17092,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:27.323713Z</t>
+          <t>2026-08-01T23:52:04.626307Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -16780,13 +17102,13 @@
       </c>
       <c r="BJ57" s="25" t="n"/>
       <c r="BK57" s="26" t="n">
-        <v>-1567</v>
+        <v>104</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.063816</v>
+        <v>2.04</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.940012</v>
+        <v>0.490196</v>
       </c>
       <c r="BN57" s="28" t="n"/>
       <c r="BO57" s="28" t="n"/>
@@ -16820,22 +17142,22 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>24b7a9fa278a4abd</t>
+          <t>6faae02228ba477e</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:00Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>401850609</t>
+          <t>761706</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -16845,12 +17167,12 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
@@ -16860,7 +17182,7 @@
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J58" s="25" t="n"/>
@@ -16870,25 +17192,25 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.4</v>
+        <v>0.460829</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.458041</v>
       </c>
       <c r="P58" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q58" s="28" t="n">
-        <v>0.135916</v>
+        <v>-0.002788</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S58" s="29" t="n">
         <v>1</v>
@@ -16900,21 +17222,35 @@
       </c>
       <c r="U58" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V58" s="24" t="n"/>
-      <c r="W58" s="26" t="n"/>
-      <c r="X58" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W58" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X58" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y58" s="25" t="n"/>
       <c r="Z58" s="26" t="n"/>
       <c r="AA58" s="28" t="n"/>
       <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n"/>
-      <c r="AD58" s="24" t="n"/>
+      <c r="AC58" s="30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:19.661895Z</t>
+        </is>
+      </c>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4000 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
+          <t>Poisson-DC rates 1.49 (home) / 1.87 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-mls-skc-hou-2026-08-01-hou).</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -16955,32 +17291,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Houston Dynamo FC</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Sporting Kansas City</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -17033,7 +17369,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:28.913495Z</t>
+          <t>2026-08-01T23:52:06.344991Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17043,13 +17379,13 @@
       </c>
       <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.4</v>
+        <v>0.460829</v>
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
@@ -17083,22 +17419,22 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>1e2e470844a24331</t>
+          <t>cc6b8b218f134422</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:30Z</t>
+          <t>2026-08-02T00:30Z</t>
         </is>
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>401850607</t>
+          <t>761705</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -17108,12 +17444,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -17133,51 +17469,65 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-156</v>
+        <v>100</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.641026</v>
+        <v>2</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.5</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.414794</v>
+        <v>0.416937</v>
       </c>
       <c r="P59" s="28" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="Q59" s="28" t="n">
-        <v>-0.194581</v>
+        <v>-0.083063</v>
       </c>
       <c r="R59" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S59" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T59" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U59" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V59" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W59" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T59" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U59" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V59" s="24" t="n"/>
-      <c r="W59" s="26" t="n"/>
-      <c r="X59" s="26" t="n"/>
+      <c r="X59" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y59" s="25" t="n"/>
       <c r="Z59" s="26" t="n"/>
       <c r="AA59" s="28" t="n"/>
       <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n"/>
-      <c r="AD59" s="24" t="n"/>
+      <c r="AC59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:20.027864Z</t>
+        </is>
+      </c>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6100 (atc-pdc-unc-hua-2026-08-02-unc).</t>
+          <t>Poisson-DC rates 1.71 (home) / 1.51 (away) from EWMA attack/defense strengths. Executable ask 0.5000 (atc-mls-stl-rsl-2026-08-01-stl).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -17218,32 +17568,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>St. Louis CITY SC</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -17296,7 +17646,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:28.912183Z</t>
+          <t>2026-08-01T23:52:07.835197Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -17306,13 +17656,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>-156</v>
+        <v>100</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.641026</v>
+        <v>2</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.5</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -17346,22 +17696,22 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>c0febd2e28b041e9</t>
+          <t>22f0f340d5054823</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:00Z</t>
+          <t>2026-08-02T01:30Z</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>401872734</t>
+          <t>761707</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -17371,12 +17721,12 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
@@ -17396,51 +17746,65 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>-245</v>
+        <v>-127</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>1.408163</v>
+        <v>1.787402</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.710145</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.6000259999999999</v>
       </c>
       <c r="P60" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q60" s="28" t="n">
-        <v>-0.174229</v>
+        <v>0.040555</v>
       </c>
       <c r="R60" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S60" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T60" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U60" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V60" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W60" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="29" t="n">
+      <c r="X60" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T60" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U60" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V60" s="24" t="n"/>
-      <c r="W60" s="26" t="n"/>
-      <c r="X60" s="26" t="n"/>
       <c r="Y60" s="25" t="n"/>
       <c r="Z60" s="26" t="n"/>
       <c r="AA60" s="28" t="n"/>
       <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n"/>
-      <c r="AD60" s="24" t="n"/>
+      <c r="AC60" s="30" t="n">
+        <v>1.1811</v>
+      </c>
+      <c r="AD60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:26:21.937064Z</t>
+        </is>
+      </c>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.7100 (atc-uru1-rcm-bri-2026-08-02-rcm).</t>
+          <t>Poisson-DC rates 2.28 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-mls-col-aus-2026-08-01-col).</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -17481,32 +17845,32 @@
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -17559,7 +17923,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:29.944986Z</t>
+          <t>2026-08-01T23:52:09.543896Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -17569,13 +17933,13 @@
       </c>
       <c r="BJ60" s="25" t="n"/>
       <c r="BK60" s="26" t="n">
-        <v>-245</v>
+        <v>-127</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>1.408163</v>
+        <v>1.787402</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.710145</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
@@ -17609,22 +17973,22 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>3a686996b93b4d7c</t>
+          <t>17c41ca1fdf74770</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:30Z</t>
+          <t>2026-08-02T02:30Z</t>
         </is>
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>401859644</t>
+          <t>761709</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -17634,12 +17998,12 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -17649,7 +18013,7 @@
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J61" s="25" t="n"/>
@@ -17659,51 +18023,65 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-178</v>
+        <v>186</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.86</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.34965</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.38746</v>
       </c>
       <c r="P61" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q61" s="28" t="n">
-        <v>-0.184153</v>
+        <v>0.03781</v>
       </c>
       <c r="R61" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S61" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T61" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U61" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V61" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W61" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T61" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U61" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V61" s="24" t="n"/>
-      <c r="W61" s="26" t="n"/>
-      <c r="X61" s="26" t="n"/>
+      <c r="X61" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y61" s="25" t="n"/>
       <c r="Z61" s="26" t="n"/>
       <c r="AA61" s="28" t="n"/>
       <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n"/>
-      <c r="AD61" s="24" t="n"/>
+      <c r="AC61" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T05:39:25.608387Z</t>
+        </is>
+      </c>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6400 (atc-ecu1-mac-gua-2026-08-02-mac).</t>
+          <t>Poisson-DC rates 1.76 (home) / 1.79 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-mls-lag-dal-2026-08-01-dal).</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -17744,32 +18122,32 @@
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -17822,7 +18200,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:30.440065Z</t>
+          <t>2026-08-01T23:52:11.231740Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -17832,13 +18210,13 @@
       </c>
       <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
-        <v>-178</v>
+        <v>186</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.86</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.34965</v>
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
@@ -17872,22 +18250,22 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>1f5c27cff77f4a3b</t>
+          <t>6a04218c09a84664</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T23:10Z</t>
+          <t>2026-08-02T02:45Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>401859718</t>
+          <t>761708</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -17897,12 +18275,12 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
@@ -17912,7 +18290,7 @@
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J62" s="25" t="n"/>
@@ -17922,51 +18300,65 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.469484</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.406677</v>
+        <v>0.432832</v>
       </c>
       <c r="P62" s="28" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>0.026449</v>
+        <v>-0.036652</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S62" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T62" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U62" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V62" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W62" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T62" s="24" t="inlineStr">
-        <is>
-          <t>soccer-poisson-dc-v1</t>
-        </is>
-      </c>
-      <c r="U62" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V62" s="24" t="n"/>
-      <c r="W62" s="26" t="n"/>
-      <c r="X62" s="26" t="n"/>
+      <c r="X62" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y62" s="25" t="n"/>
       <c r="Z62" s="26" t="n"/>
       <c r="AA62" s="28" t="n"/>
       <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
-      <c r="AD62" s="24" t="n"/>
+      <c r="AC62" s="30" t="n">
+        <v>1.4125</v>
+      </c>
+      <c r="AD62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T05:39:26.164706Z</t>
+        </is>
+      </c>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3800 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
+          <t>Poisson-DC rates 1.85 (home) / 1.59 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-mls-por-sea-2026-08-01-por).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -18007,32 +18399,32 @@
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Seattle Sounders FC</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -18085,7 +18477,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:30.884357Z</t>
+          <t>2026-08-01T23:52:12.696180Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18095,13 +18487,13 @@
       </c>
       <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>2.63</v>
+        <v>2.13</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.469484</v>
       </c>
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
@@ -18135,22 +18527,22 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>d1bd56f6a3e54db6</t>
+          <t>3d7c6e251fde488b</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-01T23:53:24.455746Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T12:30Z</t>
+          <t>2026-08-02T00:00Z</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>401886552</t>
+          <t>401859646</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -18160,12 +18552,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -18175,7 +18567,7 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J63" s="25" t="n"/>
@@ -18185,22 +18577,22 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>-2400</v>
+        <v>133</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>1.041667</v>
+        <v>2.33</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.96</v>
+        <v>0.429185</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.515227</v>
+        <v>0.456135</v>
       </c>
       <c r="P63" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>-0.444773</v>
+        <v>0.02695</v>
       </c>
       <c r="R63" s="26" t="n">
         <v>0</v>
@@ -18215,21 +18607,35 @@
       </c>
       <c r="U63" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V63" s="24" t="n"/>
-      <c r="W63" s="26" t="n"/>
-      <c r="X63" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V63" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W63" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X63" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y63" s="25" t="n"/>
       <c r="Z63" s="26" t="n"/>
       <c r="AA63" s="28" t="n"/>
       <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="30" t="n"/>
-      <c r="AD63" s="24" t="n"/>
+      <c r="AC63" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:22.035170Z</t>
+        </is>
+      </c>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.9600 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4300 (atc-ecu1-cse-sda-2026-08-01-cse).</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -18239,7 +18645,7 @@
       </c>
       <c r="AG63" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH63" s="24" t="n"/>
@@ -18270,32 +18676,32 @@
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -18348,7 +18754,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:32.406187Z</t>
+          <t>2026-08-01T23:52:16.427787Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -18358,13 +18764,13 @@
       </c>
       <c r="BJ63" s="25" t="n"/>
       <c r="BK63" s="26" t="n">
-        <v>-2400</v>
+        <v>133</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>1.041667</v>
+        <v>2.33</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.96</v>
+        <v>0.429185</v>
       </c>
       <c r="BN63" s="28" t="n"/>
       <c r="BO63" s="28" t="n"/>
@@ -18398,22 +18804,22 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>f919805677d44165</t>
+          <t>c9400950ec6e4be2</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-02T07:14:17.312478Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00Z</t>
+          <t>2026-08-02T17:30Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401886551</t>
+          <t>401841470</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -18423,12 +18829,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -18448,28 +18854,28 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-2400</v>
+        <v>223</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>1.041667</v>
+        <v>3.23</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.96</v>
+        <v>0.309598</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.575359</v>
+        <v>0.456135</v>
       </c>
       <c r="P64" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>-0.384641</v>
+        <v>0.146537</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
@@ -18492,7 +18898,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.9600 (atc-clbf-fey-ata-2026-08-02-fey).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3100 (atc-lpa-ald-gim-2026-08-02-ald).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -18533,32 +18939,32 @@
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -18611,7 +19017,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:32.414175Z</t>
+          <t>2026-08-02T07:11:22.045184Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -18621,13 +19027,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>-2400</v>
+        <v>223</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>1.041667</v>
+        <v>3.23</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.96</v>
+        <v>0.309598</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -18661,22 +19067,22 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>71a86745283e4e37</t>
+          <t>2a1b486a4ebc490b</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-02T07:14:17.312478Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T14:30Z</t>
+          <t>2026-08-02T20:00Z</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>401898711</t>
+          <t>401841473</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -18686,12 +19092,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -18711,22 +19117,22 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-2400</v>
+        <v>285</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.041667</v>
+        <v>3.85</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.96</v>
+        <v>0.25974</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.395816</v>
+        <v>0.398039</v>
       </c>
       <c r="P65" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>-0.564184</v>
+        <v>0.138299</v>
       </c>
       <c r="R65" s="26" t="n">
         <v>0</v>
@@ -18755,7 +19161,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.9600 (atc-clbf-tra-udi-2026-08-02-tra).</t>
+          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2600 (atc-lpa-new-boc-2026-08-02-new).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -18796,32 +19202,32 @@
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -18874,7 +19280,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:32.918025Z</t>
+          <t>2026-08-02T07:11:22.065186Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -18884,13 +19290,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-2400</v>
+        <v>285</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.041667</v>
+        <v>3.85</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.96</v>
+        <v>0.25974</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -18924,22 +19330,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>09af9e6bd1ef4002</t>
+          <t>c7547a2b575d4b98</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-02T07:14:17.312478Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:00Z</t>
+          <t>2026-08-02T22:15Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401897751</t>
+          <t>401841476</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -18949,12 +19355,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -18974,28 +19380,28 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.480769</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.395592</v>
+        <v>0.5359159999999999</v>
       </c>
       <c r="P66" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>-0.073892</v>
+        <v>0.055147</v>
       </c>
       <c r="R66" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S66" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
@@ -19018,7 +19424,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.40 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-clbf-sun-wre-2026-08-02-sun).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4800 (atc-lpa-riv-ros-2026-08-02-riv).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -19059,32 +19465,32 @@
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -19137,7 +19543,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:32.887246Z</t>
+          <t>2026-08-02T07:11:22.485293Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19147,13 +19553,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.480769</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -19187,22 +19593,22 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>2e6cb5ecea964b03</t>
+          <t>466587062ce646b6</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:22:40.310073Z</t>
+          <t>2026-08-02T07:14:17.312478Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:00Z</t>
+          <t>2026-08-02T18:00Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401863533</t>
+          <t>401844015</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -19212,12 +19618,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -19237,22 +19643,22 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-127</v>
+        <v>122</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.22</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.45045</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.482992</v>
+        <v>0.456135</v>
       </c>
       <c r="P67" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>-0.07647900000000001</v>
+        <v>0.005685</v>
       </c>
       <c r="R67" s="26" t="n">
         <v>0</v>
@@ -19281,7 +19687,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.69 (home) / 1.17 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-clbf-lfc-lee-2026-08-02-lfc).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-arg2-cjh-caa-2026-08-01-cjh).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -19322,32 +19728,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -19400,7 +19806,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:19:33.390319Z</t>
+          <t>2026-08-02T07:11:23.168431Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19410,13 +19816,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>-127</v>
+        <v>122</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.22</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.45045</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -19447,6 +19853,3951 @@
       <c r="CN67" s="24" t="n"/>
       <c r="CO67" s="24" t="n"/>
     </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>29b1bddb382047e4</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>401844019</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J68" s="25" t="n"/>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M68" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P68" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q68" s="28" t="n">
+        <v>0.08576499999999999</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="25" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="30" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3700 (atc-arg2-ste-casm-2026-08-02-ste).</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:23.717602Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="25" t="n"/>
+      <c r="BK68" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL68" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN68" s="28" t="n"/>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="25" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+      <c r="CB68" s="24" t="n"/>
+      <c r="CC68" s="24" t="n"/>
+      <c r="CD68" s="24" t="n"/>
+      <c r="CE68" s="24" t="n"/>
+      <c r="CF68" s="24" t="n"/>
+      <c r="CG68" s="24" t="n"/>
+      <c r="CH68" s="24" t="n"/>
+      <c r="CI68" s="24" t="n"/>
+      <c r="CJ68" s="24" t="n"/>
+      <c r="CK68" s="24" t="n"/>
+      <c r="CL68" s="24" t="n"/>
+      <c r="CM68" s="24" t="n"/>
+      <c r="CN68" s="24" t="n"/>
+      <c r="CO68" s="24" t="n"/>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>1061ca03f0c14b38</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J69" s="25" t="n"/>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M69" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O69" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P69" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q69" s="28" t="n">
+        <v>-0.004694</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U69" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="25" t="n"/>
+      <c r="Z69" s="26" t="n"/>
+      <c r="AA69" s="28" t="n"/>
+      <c r="AB69" s="28" t="n"/>
+      <c r="AC69" s="30" t="n"/>
+      <c r="AD69" s="24" t="n"/>
+      <c r="AE69" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-cat-gyt-2026-08-02-cat).</t>
+        </is>
+      </c>
+      <c r="AF69" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG69" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH69" s="24" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL69" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN69" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO69" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP69" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="AQ69" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="AR69" s="24" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="AS69" s="24" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="AT69" s="24" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="AU69" s="24" t="inlineStr">
+        <is>
+          <t>Temperley</t>
+        </is>
+      </c>
+      <c r="AV69" s="24" t="n"/>
+      <c r="AW69" s="24" t="n"/>
+      <c r="AX69" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY69" s="24" t="n"/>
+      <c r="AZ69" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA69" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB69" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC69" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD69" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE69" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG69" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:23.676456Z</t>
+        </is>
+      </c>
+      <c r="BI69" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ69" s="25" t="n"/>
+      <c r="BK69" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL69" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM69" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN69" s="28" t="n"/>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="25" t="n"/>
+      <c r="BQ69" s="27" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
+      <c r="BT69" s="28" t="n"/>
+      <c r="BU69" s="25" t="n"/>
+      <c r="BV69" s="29" t="n"/>
+      <c r="BW69" s="24" t="n"/>
+      <c r="BX69" s="30" t="n"/>
+      <c r="BY69" s="27" t="n"/>
+      <c r="BZ69" s="24" t="n"/>
+      <c r="CA69" s="31" t="n"/>
+      <c r="CB69" s="24" t="n"/>
+      <c r="CC69" s="24" t="n"/>
+      <c r="CD69" s="24" t="n"/>
+      <c r="CE69" s="24" t="n"/>
+      <c r="CF69" s="24" t="n"/>
+      <c r="CG69" s="24" t="n"/>
+      <c r="CH69" s="24" t="n"/>
+      <c r="CI69" s="24" t="n"/>
+      <c r="CJ69" s="24" t="n"/>
+      <c r="CK69" s="24" t="n"/>
+      <c r="CL69" s="24" t="n"/>
+      <c r="CM69" s="24" t="n"/>
+      <c r="CN69" s="24" t="n"/>
+      <c r="CO69" s="24" t="n"/>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>9ccc51ded5b64e42</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J70" s="25" t="n"/>
+      <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M70" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N70" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O70" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P70" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q70" s="28" t="n">
+        <v>-0.053669</v>
+      </c>
+      <c r="R70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U70" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V70" s="24" t="n"/>
+      <c r="W70" s="26" t="n"/>
+      <c r="X70" s="26" t="n"/>
+      <c r="Y70" s="25" t="n"/>
+      <c r="Z70" s="26" t="n"/>
+      <c r="AA70" s="28" t="n"/>
+      <c r="AB70" s="28" t="n"/>
+      <c r="AC70" s="30" t="n"/>
+      <c r="AD70" s="24" t="n"/>
+      <c r="AE70" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-arg2-dma-abo-2026-08-02-dma).</t>
+        </is>
+      </c>
+      <c r="AF70" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG70" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH70" s="24" t="n"/>
+      <c r="AI70" s="31" t="n"/>
+      <c r="AJ70" s="31" t="n"/>
+      <c r="AK70" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM70" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN70" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO70" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP70" s="24" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="AQ70" s="24" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="AR70" s="24" t="inlineStr">
+        <is>
+          <t>All Boys</t>
+        </is>
+      </c>
+      <c r="AS70" s="24" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="AT70" s="24" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="AU70" s="24" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="AV70" s="24" t="n"/>
+      <c r="AW70" s="24" t="n"/>
+      <c r="AX70" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY70" s="24" t="n"/>
+      <c r="AZ70" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA70" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB70" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC70" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD70" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE70" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG70" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:24.238512Z</t>
+        </is>
+      </c>
+      <c r="BI70" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ70" s="25" t="n"/>
+      <c r="BK70" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL70" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM70" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN70" s="28" t="n"/>
+      <c r="BO70" s="28" t="n"/>
+      <c r="BP70" s="25" t="n"/>
+      <c r="BQ70" s="27" t="n"/>
+      <c r="BR70" s="28" t="n"/>
+      <c r="BS70" s="28" t="n"/>
+      <c r="BT70" s="28" t="n"/>
+      <c r="BU70" s="25" t="n"/>
+      <c r="BV70" s="29" t="n"/>
+      <c r="BW70" s="24" t="n"/>
+      <c r="BX70" s="30" t="n"/>
+      <c r="BY70" s="27" t="n"/>
+      <c r="BZ70" s="24" t="n"/>
+      <c r="CA70" s="31" t="n"/>
+      <c r="CB70" s="24" t="n"/>
+      <c r="CC70" s="24" t="n"/>
+      <c r="CD70" s="24" t="n"/>
+      <c r="CE70" s="24" t="n"/>
+      <c r="CF70" s="24" t="n"/>
+      <c r="CG70" s="24" t="n"/>
+      <c r="CH70" s="24" t="n"/>
+      <c r="CI70" s="24" t="n"/>
+      <c r="CJ70" s="24" t="n"/>
+      <c r="CK70" s="24" t="n"/>
+      <c r="CL70" s="24" t="n"/>
+      <c r="CM70" s="24" t="n"/>
+      <c r="CN70" s="24" t="n"/>
+      <c r="CO70" s="24" t="n"/>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>c2ec3b63a2c44a7e</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J71" s="25" t="n"/>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M71" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P71" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q71" s="28" t="n">
+        <v>0.09642299999999999</v>
+      </c>
+      <c r="R71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="n"/>
+      <c r="W71" s="26" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="25" t="n"/>
+      <c r="Z71" s="26" t="n"/>
+      <c r="AA71" s="28" t="n"/>
+      <c r="AB71" s="28" t="n"/>
+      <c r="AC71" s="30" t="n"/>
+      <c r="AD71" s="24" t="n"/>
+      <c r="AE71" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
+        </is>
+      </c>
+      <c r="AF71" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG71" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH71" s="24" t="n"/>
+      <c r="AI71" s="31" t="n"/>
+      <c r="AJ71" s="31" t="n"/>
+      <c r="AK71" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL71" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM71" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN71" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO71" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP71" s="24" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="AQ71" s="24" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="AR71" s="24" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="AS71" s="24" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="AT71" s="24" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="AU71" s="24" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="AV71" s="24" t="n"/>
+      <c r="AW71" s="24" t="n"/>
+      <c r="AX71" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY71" s="24" t="n"/>
+      <c r="AZ71" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA71" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB71" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC71" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD71" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE71" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG71" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:24.757447Z</t>
+        </is>
+      </c>
+      <c r="BI71" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ71" s="25" t="n"/>
+      <c r="BK71" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL71" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM71" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN71" s="28" t="n"/>
+      <c r="BO71" s="28" t="n"/>
+      <c r="BP71" s="25" t="n"/>
+      <c r="BQ71" s="27" t="n"/>
+      <c r="BR71" s="28" t="n"/>
+      <c r="BS71" s="28" t="n"/>
+      <c r="BT71" s="28" t="n"/>
+      <c r="BU71" s="25" t="n"/>
+      <c r="BV71" s="29" t="n"/>
+      <c r="BW71" s="24" t="n"/>
+      <c r="BX71" s="30" t="n"/>
+      <c r="BY71" s="27" t="n"/>
+      <c r="BZ71" s="24" t="n"/>
+      <c r="CA71" s="31" t="n"/>
+      <c r="CB71" s="24" t="n"/>
+      <c r="CC71" s="24" t="n"/>
+      <c r="CD71" s="24" t="n"/>
+      <c r="CE71" s="24" t="n"/>
+      <c r="CF71" s="24" t="n"/>
+      <c r="CG71" s="24" t="n"/>
+      <c r="CH71" s="24" t="n"/>
+      <c r="CI71" s="24" t="n"/>
+      <c r="CJ71" s="24" t="n"/>
+      <c r="CK71" s="24" t="n"/>
+      <c r="CL71" s="24" t="n"/>
+      <c r="CM71" s="24" t="n"/>
+      <c r="CN71" s="24" t="n"/>
+      <c r="CO71" s="24" t="n"/>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>a0d24a75874a4152</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J72" s="25" t="n"/>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M72" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N72" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O72" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P72" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q72" s="28" t="n">
+        <v>-0.004694</v>
+      </c>
+      <c r="R72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U72" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V72" s="24" t="n"/>
+      <c r="W72" s="26" t="n"/>
+      <c r="X72" s="26" t="n"/>
+      <c r="Y72" s="25" t="n"/>
+      <c r="Z72" s="26" t="n"/>
+      <c r="AA72" s="28" t="n"/>
+      <c r="AB72" s="28" t="n"/>
+      <c r="AC72" s="30" t="n"/>
+      <c r="AD72" s="24" t="n"/>
+      <c r="AE72" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lco-san-onc-2026-08-02-san).</t>
+        </is>
+      </c>
+      <c r="AF72" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG72" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH72" s="24" t="n"/>
+      <c r="AI72" s="31" t="n"/>
+      <c r="AJ72" s="31" t="n"/>
+      <c r="AK72" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM72" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN72" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO72" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP72" s="24" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="AQ72" s="24" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="AR72" s="24" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="AS72" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="AT72" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="AU72" s="24" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="AV72" s="24" t="n"/>
+      <c r="AW72" s="24" t="n"/>
+      <c r="AX72" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY72" s="24" t="n"/>
+      <c r="AZ72" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA72" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB72" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC72" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD72" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE72" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG72" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:25.306877Z</t>
+        </is>
+      </c>
+      <c r="BI72" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ72" s="25" t="n"/>
+      <c r="BK72" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL72" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM72" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN72" s="28" t="n"/>
+      <c r="BO72" s="28" t="n"/>
+      <c r="BP72" s="25" t="n"/>
+      <c r="BQ72" s="27" t="n"/>
+      <c r="BR72" s="28" t="n"/>
+      <c r="BS72" s="28" t="n"/>
+      <c r="BT72" s="28" t="n"/>
+      <c r="BU72" s="25" t="n"/>
+      <c r="BV72" s="29" t="n"/>
+      <c r="BW72" s="24" t="n"/>
+      <c r="BX72" s="30" t="n"/>
+      <c r="BY72" s="27" t="n"/>
+      <c r="BZ72" s="24" t="n"/>
+      <c r="CA72" s="31" t="n"/>
+      <c r="CB72" s="24" t="n"/>
+      <c r="CC72" s="24" t="n"/>
+      <c r="CD72" s="24" t="n"/>
+      <c r="CE72" s="24" t="n"/>
+      <c r="CF72" s="24" t="n"/>
+      <c r="CG72" s="24" t="n"/>
+      <c r="CH72" s="24" t="n"/>
+      <c r="CI72" s="24" t="n"/>
+      <c r="CJ72" s="24" t="n"/>
+      <c r="CK72" s="24" t="n"/>
+      <c r="CL72" s="24" t="n"/>
+      <c r="CM72" s="24" t="n"/>
+      <c r="CN72" s="24" t="n"/>
+      <c r="CO72" s="24" t="n"/>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>1a4fb694c4484362</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J73" s="25" t="n"/>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M73" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O73" s="28" t="n">
+        <v>0.5359159999999999</v>
+      </c>
+      <c r="P73" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q73" s="28" t="n">
+        <v>0.12608</v>
+      </c>
+      <c r="R73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U73" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V73" s="24" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
+      <c r="Y73" s="25" t="n"/>
+      <c r="Z73" s="26" t="n"/>
+      <c r="AA73" s="28" t="n"/>
+      <c r="AB73" s="28" t="n"/>
+      <c r="AC73" s="30" t="n"/>
+      <c r="AD73" s="24" t="n"/>
+      <c r="AE73" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
+        </is>
+      </c>
+      <c r="AF73" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG73" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH73" s="24" t="n"/>
+      <c r="AI73" s="31" t="n"/>
+      <c r="AJ73" s="31" t="n"/>
+      <c r="AK73" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL73" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM73" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN73" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO73" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP73" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="AQ73" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="AR73" s="24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="AS73" s="24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="AT73" s="24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="AU73" s="24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="AV73" s="24" t="n"/>
+      <c r="AW73" s="24" t="n"/>
+      <c r="AX73" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY73" s="24" t="n"/>
+      <c r="AZ73" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA73" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB73" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC73" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD73" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE73" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG73" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:26.361618Z</t>
+        </is>
+      </c>
+      <c r="BI73" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ73" s="25" t="n"/>
+      <c r="BK73" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL73" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM73" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN73" s="28" t="n"/>
+      <c r="BO73" s="28" t="n"/>
+      <c r="BP73" s="25" t="n"/>
+      <c r="BQ73" s="27" t="n"/>
+      <c r="BR73" s="28" t="n"/>
+      <c r="BS73" s="28" t="n"/>
+      <c r="BT73" s="28" t="n"/>
+      <c r="BU73" s="25" t="n"/>
+      <c r="BV73" s="29" t="n"/>
+      <c r="BW73" s="24" t="n"/>
+      <c r="BX73" s="30" t="n"/>
+      <c r="BY73" s="27" t="n"/>
+      <c r="BZ73" s="24" t="n"/>
+      <c r="CA73" s="31" t="n"/>
+      <c r="CB73" s="24" t="n"/>
+      <c r="CC73" s="24" t="n"/>
+      <c r="CD73" s="24" t="n"/>
+      <c r="CE73" s="24" t="n"/>
+      <c r="CF73" s="24" t="n"/>
+      <c r="CG73" s="24" t="n"/>
+      <c r="CH73" s="24" t="n"/>
+      <c r="CI73" s="24" t="n"/>
+      <c r="CJ73" s="24" t="n"/>
+      <c r="CK73" s="24" t="n"/>
+      <c r="CL73" s="24" t="n"/>
+      <c r="CM73" s="24" t="n"/>
+      <c r="CN73" s="24" t="n"/>
+      <c r="CO73" s="24" t="n"/>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>e3926941fac3443a</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J74" s="25" t="n"/>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M74" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N74" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O74" s="28" t="n">
+        <v>0.414794</v>
+      </c>
+      <c r="P74" s="28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q74" s="28" t="n">
+        <v>-0.204978</v>
+      </c>
+      <c r="R74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U74" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V74" s="24" t="n"/>
+      <c r="W74" s="26" t="n"/>
+      <c r="X74" s="26" t="n"/>
+      <c r="Y74" s="25" t="n"/>
+      <c r="Z74" s="26" t="n"/>
+      <c r="AA74" s="28" t="n"/>
+      <c r="AB74" s="28" t="n"/>
+      <c r="AC74" s="30" t="n"/>
+      <c r="AD74" s="24" t="n"/>
+      <c r="AE74" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6200 (atc-pdc-unc-hua-2026-08-02-unc).</t>
+        </is>
+      </c>
+      <c r="AF74" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG74" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH74" s="24" t="n"/>
+      <c r="AI74" s="31" t="n"/>
+      <c r="AJ74" s="31" t="n"/>
+      <c r="AK74" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM74" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN74" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO74" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP74" s="24" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="AQ74" s="24" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="AR74" s="24" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="AS74" s="24" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="AT74" s="24" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="AU74" s="24" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="AV74" s="24" t="n"/>
+      <c r="AW74" s="24" t="n"/>
+      <c r="AX74" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY74" s="24" t="n"/>
+      <c r="AZ74" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA74" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB74" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC74" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD74" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE74" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG74" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:26.390990Z</t>
+        </is>
+      </c>
+      <c r="BI74" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ74" s="25" t="n"/>
+      <c r="BK74" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL74" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM74" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN74" s="28" t="n"/>
+      <c r="BO74" s="28" t="n"/>
+      <c r="BP74" s="25" t="n"/>
+      <c r="BQ74" s="27" t="n"/>
+      <c r="BR74" s="28" t="n"/>
+      <c r="BS74" s="28" t="n"/>
+      <c r="BT74" s="28" t="n"/>
+      <c r="BU74" s="25" t="n"/>
+      <c r="BV74" s="29" t="n"/>
+      <c r="BW74" s="24" t="n"/>
+      <c r="BX74" s="30" t="n"/>
+      <c r="BY74" s="27" t="n"/>
+      <c r="BZ74" s="24" t="n"/>
+      <c r="CA74" s="31" t="n"/>
+      <c r="CB74" s="24" t="n"/>
+      <c r="CC74" s="24" t="n"/>
+      <c r="CD74" s="24" t="n"/>
+      <c r="CE74" s="24" t="n"/>
+      <c r="CF74" s="24" t="n"/>
+      <c r="CG74" s="24" t="n"/>
+      <c r="CH74" s="24" t="n"/>
+      <c r="CI74" s="24" t="n"/>
+      <c r="CJ74" s="24" t="n"/>
+      <c r="CK74" s="24" t="n"/>
+      <c r="CL74" s="24" t="n"/>
+      <c r="CM74" s="24" t="n"/>
+      <c r="CN74" s="24" t="n"/>
+      <c r="CO74" s="24" t="n"/>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>98e903f5c1d5447a</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:00Z</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>401872734</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J75" s="25" t="n"/>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M75" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>0.5359159999999999</v>
+      </c>
+      <c r="P75" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q75" s="28" t="n">
+        <v>-0.023555</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U75" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="25" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="28" t="n"/>
+      <c r="AB75" s="28" t="n"/>
+      <c r="AC75" s="30" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-uru1-rcm-bri-2026-08-02-rcm).</t>
+        </is>
+      </c>
+      <c r="AF75" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG75" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="31" t="n"/>
+      <c r="AK75" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL75" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN75" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO75" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP75" s="24" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="AQ75" s="24" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="AR75" s="24" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="AS75" s="24" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="AT75" s="24" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="AU75" s="24" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA75" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB75" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC75" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD75" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE75" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG75" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:27.403873Z</t>
+        </is>
+      </c>
+      <c r="BI75" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ75" s="25" t="n"/>
+      <c r="BK75" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL75" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM75" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN75" s="28" t="n"/>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="25" t="n"/>
+      <c r="BQ75" s="27" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
+      <c r="BT75" s="28" t="n"/>
+      <c r="BU75" s="25" t="n"/>
+      <c r="BV75" s="29" t="n"/>
+      <c r="BW75" s="24" t="n"/>
+      <c r="BX75" s="30" t="n"/>
+      <c r="BY75" s="27" t="n"/>
+      <c r="BZ75" s="24" t="n"/>
+      <c r="CA75" s="31" t="n"/>
+      <c r="CB75" s="24" t="n"/>
+      <c r="CC75" s="24" t="n"/>
+      <c r="CD75" s="24" t="n"/>
+      <c r="CE75" s="24" t="n"/>
+      <c r="CF75" s="24" t="n"/>
+      <c r="CG75" s="24" t="n"/>
+      <c r="CH75" s="24" t="n"/>
+      <c r="CI75" s="24" t="n"/>
+      <c r="CJ75" s="24" t="n"/>
+      <c r="CK75" s="24" t="n"/>
+      <c r="CL75" s="24" t="n"/>
+      <c r="CM75" s="24" t="n"/>
+      <c r="CN75" s="24" t="n"/>
+      <c r="CO75" s="24" t="n"/>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>270463370f8f41dd</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J76" s="25" t="n"/>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M76" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N76" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O76" s="28" t="n">
+        <v>0.456135</v>
+      </c>
+      <c r="P76" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q76" s="28" t="n">
+        <v>-0.194215</v>
+      </c>
+      <c r="R76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U76" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V76" s="24" t="n"/>
+      <c r="W76" s="26" t="n"/>
+      <c r="X76" s="26" t="n"/>
+      <c r="Y76" s="25" t="n"/>
+      <c r="Z76" s="26" t="n"/>
+      <c r="AA76" s="28" t="n"/>
+      <c r="AB76" s="28" t="n"/>
+      <c r="AC76" s="30" t="n"/>
+      <c r="AD76" s="24" t="n"/>
+      <c r="AE76" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-ecu1-mac-gua-2026-08-02-mac).</t>
+        </is>
+      </c>
+      <c r="AF76" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG76" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH76" s="24" t="n"/>
+      <c r="AI76" s="31" t="n"/>
+      <c r="AJ76" s="31" t="n"/>
+      <c r="AK76" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL76" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN76" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO76" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP76" s="24" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="AQ76" s="24" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="AR76" s="24" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="AS76" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AT76" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AU76" s="24" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="AV76" s="24" t="n"/>
+      <c r="AW76" s="24" t="n"/>
+      <c r="AX76" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY76" s="24" t="n"/>
+      <c r="AZ76" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA76" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB76" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC76" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD76" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE76" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF76" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG76" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:27.951055Z</t>
+        </is>
+      </c>
+      <c r="BI76" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ76" s="25" t="n"/>
+      <c r="BK76" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL76" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM76" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN76" s="28" t="n"/>
+      <c r="BO76" s="28" t="n"/>
+      <c r="BP76" s="25" t="n"/>
+      <c r="BQ76" s="27" t="n"/>
+      <c r="BR76" s="28" t="n"/>
+      <c r="BS76" s="28" t="n"/>
+      <c r="BT76" s="28" t="n"/>
+      <c r="BU76" s="25" t="n"/>
+      <c r="BV76" s="29" t="n"/>
+      <c r="BW76" s="24" t="n"/>
+      <c r="BX76" s="30" t="n"/>
+      <c r="BY76" s="27" t="n"/>
+      <c r="BZ76" s="24" t="n"/>
+      <c r="CA76" s="31" t="n"/>
+      <c r="CB76" s="24" t="n"/>
+      <c r="CC76" s="24" t="n"/>
+      <c r="CD76" s="24" t="n"/>
+      <c r="CE76" s="24" t="n"/>
+      <c r="CF76" s="24" t="n"/>
+      <c r="CG76" s="24" t="n"/>
+      <c r="CH76" s="24" t="n"/>
+      <c r="CI76" s="24" t="n"/>
+      <c r="CJ76" s="24" t="n"/>
+      <c r="CK76" s="24" t="n"/>
+      <c r="CL76" s="24" t="n"/>
+      <c r="CM76" s="24" t="n"/>
+      <c r="CN76" s="24" t="n"/>
+      <c r="CO76" s="24" t="n"/>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>f94252fdb0b648ef</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>Barcelona SC</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Leones</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J77" s="25" t="n"/>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M77" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N77" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O77" s="28" t="n">
+        <v>0.406677</v>
+      </c>
+      <c r="P77" s="28" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q77" s="28" t="n">
+        <v>0.057027</v>
+      </c>
+      <c r="R77" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U77" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="n"/>
+      <c r="W77" s="26" t="n"/>
+      <c r="X77" s="26" t="n"/>
+      <c r="Y77" s="25" t="n"/>
+      <c r="Z77" s="26" t="n"/>
+      <c r="AA77" s="28" t="n"/>
+      <c r="AB77" s="28" t="n"/>
+      <c r="AC77" s="30" t="n"/>
+      <c r="AD77" s="24" t="n"/>
+      <c r="AE77" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
+        </is>
+      </c>
+      <c r="AF77" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG77" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH77" s="24" t="n"/>
+      <c r="AI77" s="31" t="n"/>
+      <c r="AJ77" s="31" t="n"/>
+      <c r="AK77" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL77" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM77" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN77" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO77" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP77" s="24" t="inlineStr">
+        <is>
+          <t>Barcelona SC</t>
+        </is>
+      </c>
+      <c r="AQ77" s="24" t="inlineStr">
+        <is>
+          <t>Barcelona SC</t>
+        </is>
+      </c>
+      <c r="AR77" s="24" t="inlineStr">
+        <is>
+          <t>Barcelona SC</t>
+        </is>
+      </c>
+      <c r="AS77" s="24" t="inlineStr">
+        <is>
+          <t>Leones</t>
+        </is>
+      </c>
+      <c r="AT77" s="24" t="inlineStr">
+        <is>
+          <t>Leones</t>
+        </is>
+      </c>
+      <c r="AU77" s="24" t="inlineStr">
+        <is>
+          <t>Leones</t>
+        </is>
+      </c>
+      <c r="AV77" s="24" t="n"/>
+      <c r="AW77" s="24" t="n"/>
+      <c r="AX77" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY77" s="24" t="n"/>
+      <c r="AZ77" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA77" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB77" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC77" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD77" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE77" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG77" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:28.476441Z</t>
+        </is>
+      </c>
+      <c r="BI77" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ77" s="25" t="n"/>
+      <c r="BK77" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL77" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM77" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN77" s="28" t="n"/>
+      <c r="BO77" s="28" t="n"/>
+      <c r="BP77" s="25" t="n"/>
+      <c r="BQ77" s="27" t="n"/>
+      <c r="BR77" s="28" t="n"/>
+      <c r="BS77" s="28" t="n"/>
+      <c r="BT77" s="28" t="n"/>
+      <c r="BU77" s="25" t="n"/>
+      <c r="BV77" s="29" t="n"/>
+      <c r="BW77" s="24" t="n"/>
+      <c r="BX77" s="30" t="n"/>
+      <c r="BY77" s="27" t="n"/>
+      <c r="BZ77" s="24" t="n"/>
+      <c r="CA77" s="31" t="n"/>
+      <c r="CB77" s="24" t="n"/>
+      <c r="CC77" s="24" t="n"/>
+      <c r="CD77" s="24" t="n"/>
+      <c r="CE77" s="24" t="n"/>
+      <c r="CF77" s="24" t="n"/>
+      <c r="CG77" s="24" t="n"/>
+      <c r="CH77" s="24" t="n"/>
+      <c r="CI77" s="24" t="n"/>
+      <c r="CJ77" s="24" t="n"/>
+      <c r="CK77" s="24" t="n"/>
+      <c r="CL77" s="24" t="n"/>
+      <c r="CM77" s="24" t="n"/>
+      <c r="CN77" s="24" t="n"/>
+      <c r="CO77" s="24" t="n"/>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>1f9fc42417d84b57</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T12:30Z</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>401886552</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I78" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J78" s="25" t="n"/>
+      <c r="K78" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L78" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M78" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N78" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O78" s="28" t="n">
+        <v>0.515227</v>
+      </c>
+      <c r="P78" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q78" s="28" t="n">
+        <v>-0.175175</v>
+      </c>
+      <c r="R78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U78" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V78" s="24" t="n"/>
+      <c r="W78" s="26" t="n"/>
+      <c r="X78" s="26" t="n"/>
+      <c r="Y78" s="25" t="n"/>
+      <c r="Z78" s="26" t="n"/>
+      <c r="AA78" s="28" t="n"/>
+      <c r="AB78" s="28" t="n"/>
+      <c r="AC78" s="30" t="n"/>
+      <c r="AD78" s="24" t="n"/>
+      <c r="AE78" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.6900 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
+        </is>
+      </c>
+      <c r="AF78" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG78" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH78" s="24" t="n"/>
+      <c r="AI78" s="31" t="n"/>
+      <c r="AJ78" s="31" t="n"/>
+      <c r="AK78" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL78" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM78" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN78" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO78" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP78" s="24" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="AQ78" s="24" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="AR78" s="24" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="AS78" s="24" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="AT78" s="24" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="AU78" s="24" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="AV78" s="24" t="n"/>
+      <c r="AW78" s="24" t="n"/>
+      <c r="AX78" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY78" s="24" t="n"/>
+      <c r="AZ78" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA78" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB78" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC78" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD78" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE78" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF78" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG78" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH78" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:30.155770Z</t>
+        </is>
+      </c>
+      <c r="BI78" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ78" s="25" t="n"/>
+      <c r="BK78" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL78" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM78" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN78" s="28" t="n"/>
+      <c r="BO78" s="28" t="n"/>
+      <c r="BP78" s="25" t="n"/>
+      <c r="BQ78" s="27" t="n"/>
+      <c r="BR78" s="28" t="n"/>
+      <c r="BS78" s="28" t="n"/>
+      <c r="BT78" s="28" t="n"/>
+      <c r="BU78" s="25" t="n"/>
+      <c r="BV78" s="29" t="n"/>
+      <c r="BW78" s="24" t="n"/>
+      <c r="BX78" s="30" t="n"/>
+      <c r="BY78" s="27" t="n"/>
+      <c r="BZ78" s="24" t="n"/>
+      <c r="CA78" s="31" t="n"/>
+      <c r="CB78" s="24" t="n"/>
+      <c r="CC78" s="24" t="n"/>
+      <c r="CD78" s="24" t="n"/>
+      <c r="CE78" s="24" t="n"/>
+      <c r="CF78" s="24" t="n"/>
+      <c r="CG78" s="24" t="n"/>
+      <c r="CH78" s="24" t="n"/>
+      <c r="CI78" s="24" t="n"/>
+      <c r="CJ78" s="24" t="n"/>
+      <c r="CK78" s="24" t="n"/>
+      <c r="CL78" s="24" t="n"/>
+      <c r="CM78" s="24" t="n"/>
+      <c r="CN78" s="24" t="n"/>
+      <c r="CO78" s="24" t="n"/>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>18254c4246934159</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00Z</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>401886551</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J79" s="25" t="n"/>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M79" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N79" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O79" s="28" t="n">
+        <v>0.575359</v>
+      </c>
+      <c r="P79" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q79" s="28" t="n">
+        <v>0.215647</v>
+      </c>
+      <c r="R79" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S79" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T79" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U79" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V79" s="24" t="n"/>
+      <c r="W79" s="26" t="n"/>
+      <c r="X79" s="26" t="n"/>
+      <c r="Y79" s="25" t="n"/>
+      <c r="Z79" s="26" t="n"/>
+      <c r="AA79" s="28" t="n"/>
+      <c r="AB79" s="28" t="n"/>
+      <c r="AC79" s="30" t="n"/>
+      <c r="AD79" s="24" t="n"/>
+      <c r="AE79" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-clbf-fey-ata-2026-08-02-fey).</t>
+        </is>
+      </c>
+      <c r="AF79" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG79" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH79" s="24" t="n"/>
+      <c r="AI79" s="31" t="n"/>
+      <c r="AJ79" s="31" t="n"/>
+      <c r="AK79" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL79" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM79" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN79" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO79" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP79" s="24" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="AQ79" s="24" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="AR79" s="24" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="AS79" s="24" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="AT79" s="24" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="AU79" s="24" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="AV79" s="24" t="n"/>
+      <c r="AW79" s="24" t="n"/>
+      <c r="AX79" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY79" s="24" t="n"/>
+      <c r="AZ79" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA79" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB79" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC79" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD79" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE79" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG79" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:30.185486Z</t>
+        </is>
+      </c>
+      <c r="BI79" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ79" s="25" t="n"/>
+      <c r="BK79" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL79" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM79" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN79" s="28" t="n"/>
+      <c r="BO79" s="28" t="n"/>
+      <c r="BP79" s="25" t="n"/>
+      <c r="BQ79" s="27" t="n"/>
+      <c r="BR79" s="28" t="n"/>
+      <c r="BS79" s="28" t="n"/>
+      <c r="BT79" s="28" t="n"/>
+      <c r="BU79" s="25" t="n"/>
+      <c r="BV79" s="29" t="n"/>
+      <c r="BW79" s="24" t="n"/>
+      <c r="BX79" s="30" t="n"/>
+      <c r="BY79" s="27" t="n"/>
+      <c r="BZ79" s="24" t="n"/>
+      <c r="CA79" s="31" t="n"/>
+      <c r="CB79" s="24" t="n"/>
+      <c r="CC79" s="24" t="n"/>
+      <c r="CD79" s="24" t="n"/>
+      <c r="CE79" s="24" t="n"/>
+      <c r="CF79" s="24" t="n"/>
+      <c r="CG79" s="24" t="n"/>
+      <c r="CH79" s="24" t="n"/>
+      <c r="CI79" s="24" t="n"/>
+      <c r="CJ79" s="24" t="n"/>
+      <c r="CK79" s="24" t="n"/>
+      <c r="CL79" s="24" t="n"/>
+      <c r="CM79" s="24" t="n"/>
+      <c r="CN79" s="24" t="n"/>
+      <c r="CO79" s="24" t="n"/>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>2166cac2e98945a1</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T14:30Z</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>401898711</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J80" s="25" t="n"/>
+      <c r="K80" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M80" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N80" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O80" s="28" t="n">
+        <v>0.395816</v>
+      </c>
+      <c r="P80" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q80" s="28" t="n">
+        <v>-0.01402</v>
+      </c>
+      <c r="R80" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U80" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V80" s="24" t="n"/>
+      <c r="W80" s="26" t="n"/>
+      <c r="X80" s="26" t="n"/>
+      <c r="Y80" s="25" t="n"/>
+      <c r="Z80" s="26" t="n"/>
+      <c r="AA80" s="28" t="n"/>
+      <c r="AB80" s="28" t="n"/>
+      <c r="AC80" s="30" t="n"/>
+      <c r="AD80" s="24" t="n"/>
+      <c r="AE80" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-clbf-tra-udi-2026-08-02-tra).</t>
+        </is>
+      </c>
+      <c r="AF80" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG80" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH80" s="24" t="n"/>
+      <c r="AI80" s="31" t="n"/>
+      <c r="AJ80" s="31" t="n"/>
+      <c r="AK80" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL80" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM80" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN80" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO80" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP80" s="24" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="AQ80" s="24" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="AR80" s="24" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="AS80" s="24" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="AT80" s="24" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="AU80" s="24" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="AV80" s="24" t="n"/>
+      <c r="AW80" s="24" t="n"/>
+      <c r="AX80" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY80" s="24" t="n"/>
+      <c r="AZ80" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA80" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB80" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC80" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD80" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE80" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF80" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG80" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH80" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:30.672870Z</t>
+        </is>
+      </c>
+      <c r="BI80" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ80" s="25" t="n"/>
+      <c r="BK80" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL80" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM80" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN80" s="28" t="n"/>
+      <c r="BO80" s="28" t="n"/>
+      <c r="BP80" s="25" t="n"/>
+      <c r="BQ80" s="27" t="n"/>
+      <c r="BR80" s="28" t="n"/>
+      <c r="BS80" s="28" t="n"/>
+      <c r="BT80" s="28" t="n"/>
+      <c r="BU80" s="25" t="n"/>
+      <c r="BV80" s="29" t="n"/>
+      <c r="BW80" s="24" t="n"/>
+      <c r="BX80" s="30" t="n"/>
+      <c r="BY80" s="27" t="n"/>
+      <c r="BZ80" s="24" t="n"/>
+      <c r="CA80" s="31" t="n"/>
+      <c r="CB80" s="24" t="n"/>
+      <c r="CC80" s="24" t="n"/>
+      <c r="CD80" s="24" t="n"/>
+      <c r="CE80" s="24" t="n"/>
+      <c r="CF80" s="24" t="n"/>
+      <c r="CG80" s="24" t="n"/>
+      <c r="CH80" s="24" t="n"/>
+      <c r="CI80" s="24" t="n"/>
+      <c r="CJ80" s="24" t="n"/>
+      <c r="CK80" s="24" t="n"/>
+      <c r="CL80" s="24" t="n"/>
+      <c r="CM80" s="24" t="n"/>
+      <c r="CN80" s="24" t="n"/>
+      <c r="CO80" s="24" t="n"/>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>2e8f87a3b8894952</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:00Z</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>401897751</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J81" s="25" t="n"/>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M81" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N81" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O81" s="28" t="n">
+        <v>0.395592</v>
+      </c>
+      <c r="P81" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q81" s="28" t="n">
+        <v>-0.073892</v>
+      </c>
+      <c r="R81" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T81" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U81" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V81" s="24" t="n"/>
+      <c r="W81" s="26" t="n"/>
+      <c r="X81" s="26" t="n"/>
+      <c r="Y81" s="25" t="n"/>
+      <c r="Z81" s="26" t="n"/>
+      <c r="AA81" s="28" t="n"/>
+      <c r="AB81" s="28" t="n"/>
+      <c r="AC81" s="30" t="n"/>
+      <c r="AD81" s="24" t="n"/>
+      <c r="AE81" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.40 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-clbf-sun-wre-2026-08-02-sun).</t>
+        </is>
+      </c>
+      <c r="AF81" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG81" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH81" s="24" t="n"/>
+      <c r="AI81" s="31" t="n"/>
+      <c r="AJ81" s="31" t="n"/>
+      <c r="AK81" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL81" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM81" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN81" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO81" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP81" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="AQ81" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="AR81" s="24" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="AS81" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="AT81" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="AU81" s="24" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="AV81" s="24" t="n"/>
+      <c r="AW81" s="24" t="n"/>
+      <c r="AX81" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY81" s="24" t="n"/>
+      <c r="AZ81" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA81" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB81" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC81" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD81" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE81" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG81" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH81" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:30.781687Z</t>
+        </is>
+      </c>
+      <c r="BI81" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ81" s="25" t="n"/>
+      <c r="BK81" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL81" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM81" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN81" s="28" t="n"/>
+      <c r="BO81" s="28" t="n"/>
+      <c r="BP81" s="25" t="n"/>
+      <c r="BQ81" s="27" t="n"/>
+      <c r="BR81" s="28" t="n"/>
+      <c r="BS81" s="28" t="n"/>
+      <c r="BT81" s="28" t="n"/>
+      <c r="BU81" s="25" t="n"/>
+      <c r="BV81" s="29" t="n"/>
+      <c r="BW81" s="24" t="n"/>
+      <c r="BX81" s="30" t="n"/>
+      <c r="BY81" s="27" t="n"/>
+      <c r="BZ81" s="24" t="n"/>
+      <c r="CA81" s="31" t="n"/>
+      <c r="CB81" s="24" t="n"/>
+      <c r="CC81" s="24" t="n"/>
+      <c r="CD81" s="24" t="n"/>
+      <c r="CE81" s="24" t="n"/>
+      <c r="CF81" s="24" t="n"/>
+      <c r="CG81" s="24" t="n"/>
+      <c r="CH81" s="24" t="n"/>
+      <c r="CI81" s="24" t="n"/>
+      <c r="CJ81" s="24" t="n"/>
+      <c r="CK81" s="24" t="n"/>
+      <c r="CL81" s="24" t="n"/>
+      <c r="CM81" s="24" t="n"/>
+      <c r="CN81" s="24" t="n"/>
+      <c r="CO81" s="24" t="n"/>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>1b23b9ba6abf448b</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:14:17.312478Z</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>SOCCER</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J82" s="25" t="n"/>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M82" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N82" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O82" s="28" t="n">
+        <v>0.482992</v>
+      </c>
+      <c r="P82" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q82" s="28" t="n">
+        <v>-0.07647900000000001</v>
+      </c>
+      <c r="R82" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="U82" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V82" s="24" t="n"/>
+      <c r="W82" s="26" t="n"/>
+      <c r="X82" s="26" t="n"/>
+      <c r="Y82" s="25" t="n"/>
+      <c r="Z82" s="26" t="n"/>
+      <c r="AA82" s="28" t="n"/>
+      <c r="AB82" s="28" t="n"/>
+      <c r="AC82" s="30" t="n"/>
+      <c r="AD82" s="24" t="n"/>
+      <c r="AE82" s="31" t="inlineStr">
+        <is>
+          <t>Poisson-DC rates 1.69 (home) / 1.17 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-clbf-lfc-lee-2026-08-02-lfc).</t>
+        </is>
+      </c>
+      <c r="AF82" s="31" t="inlineStr">
+        <is>
+          <t>Research-only soccer score model; draw-aware, but not yet locked-holdout qualified.</t>
+        </is>
+      </c>
+      <c r="AG82" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH82" s="24" t="n"/>
+      <c r="AI82" s="31" t="n"/>
+      <c r="AJ82" s="31" t="n"/>
+      <c r="AK82" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL82" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM82" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP82" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="AQ82" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="AR82" s="24" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="AS82" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="AT82" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="AU82" s="24" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="AV82" s="24" t="n"/>
+      <c r="AW82" s="24" t="n"/>
+      <c r="AX82" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY82" s="24" t="n"/>
+      <c r="AZ82" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA82" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BB82" s="24" t="inlineStr">
+        <is>
+          <t>poisson_dixon_coles</t>
+        </is>
+      </c>
+      <c r="BC82" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BD82" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BE82" s="24" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="BF82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG82" s="24" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="BH82" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:11:31.252931Z</t>
+        </is>
+      </c>
+      <c r="BI82" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ82" s="25" t="n"/>
+      <c r="BK82" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL82" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM82" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN82" s="28" t="n"/>
+      <c r="BO82" s="28" t="n"/>
+      <c r="BP82" s="25" t="n"/>
+      <c r="BQ82" s="27" t="n"/>
+      <c r="BR82" s="28" t="n"/>
+      <c r="BS82" s="28" t="n"/>
+      <c r="BT82" s="28" t="n"/>
+      <c r="BU82" s="25" t="n"/>
+      <c r="BV82" s="29" t="n"/>
+      <c r="BW82" s="24" t="n"/>
+      <c r="BX82" s="30" t="n"/>
+      <c r="BY82" s="27" t="n"/>
+      <c r="BZ82" s="24" t="n"/>
+      <c r="CA82" s="31" t="n"/>
+      <c r="CB82" s="24" t="n"/>
+      <c r="CC82" s="24" t="n"/>
+      <c r="CD82" s="24" t="n"/>
+      <c r="CE82" s="24" t="n"/>
+      <c r="CF82" s="24" t="n"/>
+      <c r="CG82" s="24" t="n"/>
+      <c r="CH82" s="24" t="n"/>
+      <c r="CI82" s="24" t="n"/>
+      <c r="CJ82" s="24" t="n"/>
+      <c r="CK82" s="24" t="n"/>
+      <c r="CL82" s="24" t="n"/>
+      <c r="CM82" s="24" t="n"/>
+      <c r="CN82" s="24" t="n"/>
+      <c r="CO82" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -18804,12 +18804,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>c9400950ec6e4be2</t>
+          <t>55ed7995713c4be4</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -18854,13 +18854,13 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.3003</v>
       </c>
       <c r="O64" s="28" t="n">
         <v>0.456135</v>
@@ -18869,10 +18869,10 @@
         <v>0.2</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0.146537</v>
+        <v>0.155835</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S64" s="29" t="n">
         <v>1</v>
@@ -18898,7 +18898,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3100 (atc-lpa-ald-gim-2026-08-02-ald).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-lpa-ald-gim-2026-08-02-ald).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:22.045184Z</t>
+          <t>2026-08-02T08:13:25.124724Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19027,13 +19027,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.3003</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -19067,12 +19067,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>2a1b486a4ebc490b</t>
+          <t>392a2f6d67a34620</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:22.065186Z</t>
+          <t>2026-08-02T08:13:25.131583Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19330,12 +19330,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>c7547a2b575d4b98</t>
+          <t>a74b609450044b06</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:22.485293Z</t>
+          <t>2026-08-02T08:13:25.638678Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19593,12 +19593,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>466587062ce646b6</t>
+          <t>40d602f63b694901</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:23.168431Z</t>
+          <t>2026-08-02T08:13:26.192927Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19856,12 +19856,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>29b1bddb382047e4</t>
+          <t>571cbfbe79c14c25</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:23.717602Z</t>
+          <t>2026-08-02T08:13:26.834968Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20119,12 +20119,12 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>1061ca03f0c14b38</t>
+          <t>207400d6575545fb</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:23.676456Z</t>
+          <t>2026-08-02T08:13:26.808979Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20382,12 +20382,12 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>9ccc51ded5b64e42</t>
+          <t>e88f0fa338274204</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:24.238512Z</t>
+          <t>2026-08-02T08:13:27.355220Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -20645,12 +20645,12 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>c2ec3b63a2c44a7e</t>
+          <t>bc81abee15784afc</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -20695,13 +20695,13 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.37037</v>
       </c>
       <c r="O71" s="28" t="n">
         <v>0.456135</v>
@@ -20710,7 +20710,7 @@
         <v>0.2</v>
       </c>
       <c r="Q71" s="28" t="n">
-        <v>0.09642299999999999</v>
+        <v>0.08576499999999999</v>
       </c>
       <c r="R71" s="26" t="n">
         <v>0</v>
@@ -20739,7 +20739,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3700 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -20858,7 +20858,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:24.757447Z</t>
+          <t>2026-08-02T08:13:27.689892Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -20868,13 +20868,13 @@
       </c>
       <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.37037</v>
       </c>
       <c r="BN71" s="28" t="n"/>
       <c r="BO71" s="28" t="n"/>
@@ -20908,12 +20908,12 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>a0d24a75874a4152</t>
+          <t>e02d784cb60042dd</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:25.306877Z</t>
+          <t>2026-08-02T08:13:28.471107Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21171,12 +21171,12 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>1a4fb694c4484362</t>
+          <t>deda227db4bb477d</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -21221,13 +21221,13 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.4</v>
       </c>
       <c r="O73" s="28" t="n">
         <v>0.5359159999999999</v>
@@ -21236,7 +21236,7 @@
         <v>0.2</v>
       </c>
       <c r="Q73" s="28" t="n">
-        <v>0.12608</v>
+        <v>0.135916</v>
       </c>
       <c r="R73" s="26" t="n">
         <v>0</v>
@@ -21265,7 +21265,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4000 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:26.361618Z</t>
+          <t>2026-08-02T08:13:29.617042Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21394,13 +21394,13 @@
       </c>
       <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.4</v>
       </c>
       <c r="BN73" s="28" t="n"/>
       <c r="BO73" s="28" t="n"/>
@@ -21434,12 +21434,12 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>e3926941fac3443a</t>
+          <t>c3143d1900784cca</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-163</v>
+        <v>-170</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.588235</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.62963</v>
       </c>
       <c r="O74" s="28" t="n">
         <v>0.414794</v>
@@ -21499,7 +21499,7 @@
         <v>0.19</v>
       </c>
       <c r="Q74" s="28" t="n">
-        <v>-0.204978</v>
+        <v>-0.214836</v>
       </c>
       <c r="R74" s="26" t="n">
         <v>0</v>
@@ -21528,7 +21528,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6200 (atc-pdc-unc-hua-2026-08-02-unc).</t>
+          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-pdc-unc-hua-2026-08-02-unc).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:26.390990Z</t>
+          <t>2026-08-02T08:13:29.597576Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -21657,13 +21657,13 @@
       </c>
       <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>-163</v>
+        <v>-170</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.588235</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.62963</v>
       </c>
       <c r="BN74" s="28" t="n"/>
       <c r="BO74" s="28" t="n"/>
@@ -21697,12 +21697,12 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>98e903f5c1d5447a</t>
+          <t>c958fb5136a7467f</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -21910,7 +21910,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:27.403873Z</t>
+          <t>2026-08-02T08:13:30.643343Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -21960,12 +21960,12 @@
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>270463370f8f41dd</t>
+          <t>d2792e8a333f49ec</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:27.951055Z</t>
+          <t>2026-08-02T08:13:31.136989Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22223,12 +22223,12 @@
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>f94252fdb0b648ef</t>
+          <t>b0810b50b6a443b6</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
@@ -22273,13 +22273,13 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.340136</v>
       </c>
       <c r="O77" s="28" t="n">
         <v>0.406677</v>
@@ -22288,7 +22288,7 @@
         <v>0.19</v>
       </c>
       <c r="Q77" s="28" t="n">
-        <v>0.057027</v>
+        <v>0.066541</v>
       </c>
       <c r="R77" s="26" t="n">
         <v>0</v>
@@ -22317,7 +22317,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
+          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3400 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:28.476441Z</t>
+          <t>2026-08-02T08:13:31.689990Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22446,13 +22446,13 @@
       </c>
       <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.340136</v>
       </c>
       <c r="BN77" s="28" t="n"/>
       <c r="BO77" s="28" t="n"/>
@@ -22486,12 +22486,12 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>1f9fc42417d84b57</t>
+          <t>f9f5fabcb4d74d39</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -22536,13 +22536,13 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="O78" s="28" t="n">
         <v>0.515227</v>
@@ -22551,7 +22551,7 @@
         <v>0.04</v>
       </c>
       <c r="Q78" s="28" t="n">
-        <v>-0.175175</v>
+        <v>-0.184473</v>
       </c>
       <c r="R78" s="26" t="n">
         <v>0</v>
@@ -22580,7 +22580,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.6900 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
+          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.7000 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:30.155770Z</t>
+          <t>2026-08-02T08:13:33.477773Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -22709,13 +22709,13 @@
       </c>
       <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="BN78" s="28" t="n"/>
       <c r="BO78" s="28" t="n"/>
@@ -22749,12 +22749,12 @@
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>18254c4246934159</t>
+          <t>d6fcf7d09f564659</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
@@ -22799,13 +22799,13 @@
         </is>
       </c>
       <c r="L79" s="26" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M79" s="27" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="N79" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.34965</v>
       </c>
       <c r="O79" s="28" t="n">
         <v>0.575359</v>
@@ -22814,7 +22814,7 @@
         <v>0.04</v>
       </c>
       <c r="Q79" s="28" t="n">
-        <v>0.215647</v>
+        <v>0.225709</v>
       </c>
       <c r="R79" s="26" t="n">
         <v>100</v>
@@ -22843,7 +22843,7 @@
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-clbf-fey-ata-2026-08-02-fey).</t>
+          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-clbf-fey-ata-2026-08-02-fey).</t>
         </is>
       </c>
       <c r="AF79" s="31" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:30.185486Z</t>
+          <t>2026-08-02T08:13:33.464341Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -22972,13 +22972,13 @@
       </c>
       <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="BL79" s="27" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="BM79" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.34965</v>
       </c>
       <c r="BN79" s="28" t="n"/>
       <c r="BO79" s="28" t="n"/>
@@ -23012,12 +23012,12 @@
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>2166cac2e98945a1</t>
+          <t>e6c66f97d0f141ee</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:30.672870Z</t>
+          <t>2026-08-02T08:13:33.982808Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -23275,12 +23275,12 @@
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>2e8f87a3b8894952</t>
+          <t>0285ccf74ed94091</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:30.781687Z</t>
+          <t>2026-08-02T08:13:34.058807Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -23538,12 +23538,12 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>1b23b9ba6abf448b</t>
+          <t>5a11720a728f4ecd</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:14:17.312478Z</t>
+          <t>2026-08-02T08:16:59.190075Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -23588,13 +23588,13 @@
         </is>
       </c>
       <c r="L82" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="M82" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="N82" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="O82" s="28" t="n">
         <v>0.482992</v>
@@ -23603,7 +23603,7 @@
         <v>0.04</v>
       </c>
       <c r="Q82" s="28" t="n">
-        <v>-0.07647900000000001</v>
+        <v>-0.087823</v>
       </c>
       <c r="R82" s="26" t="n">
         <v>0</v>
@@ -23632,7 +23632,7 @@
       <c r="AD82" s="24" t="n"/>
       <c r="AE82" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.69 (home) / 1.17 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-clbf-lfc-lee-2026-08-02-lfc).</t>
+          <t>Poisson-DC rates 1.69 (home) / 1.17 (away) from EWMA attack/defense strengths. Executable ask 0.5700 (atc-clbf-lfc-lee-2026-08-02-lfc).</t>
         </is>
       </c>
       <c r="AF82" s="31" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:11:31.252931Z</t>
+          <t>2026-08-02T08:13:34.558949Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -23761,13 +23761,13 @@
       </c>
       <c r="BJ82" s="25" t="n"/>
       <c r="BK82" s="26" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="BL82" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.75188</v>
       </c>
       <c r="BM82" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.570815</v>
       </c>
       <c r="BN82" s="28" t="n"/>
       <c r="BO82" s="28" t="n"/>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -18804,12 +18804,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>55ed7995713c4be4</t>
+          <t>2a34a934fddc4d04</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:25.124724Z</t>
+          <t>2026-08-02T09:54:37.993984Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19067,12 +19067,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>392a2f6d67a34620</t>
+          <t>1b408477fd7d412b</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19117,13 +19117,13 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.25974</v>
+        <v>0.25</v>
       </c>
       <c r="O65" s="28" t="n">
         <v>0.398039</v>
@@ -19132,10 +19132,10 @@
         <v>0.2</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>0.138299</v>
+        <v>0.148039</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S65" s="29" t="n">
         <v>1</v>
@@ -19161,7 +19161,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2600 (atc-lpa-new-boc-2026-08-02-new).</t>
+          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2500 (atc-lpa-new-boc-2026-08-02-new).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:25.131583Z</t>
+          <t>2026-08-02T09:54:38.035675Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19290,13 +19290,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.25974</v>
+        <v>0.25</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -19330,12 +19330,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>a74b609450044b06</t>
+          <t>b3cc0a09be144952</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:25.638678Z</t>
+          <t>2026-08-02T09:54:38.550577Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19593,12 +19593,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>40d602f63b694901</t>
+          <t>e8d622bf760b47cf</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:26.192927Z</t>
+          <t>2026-08-02T09:54:39.105773Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19856,12 +19856,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>571cbfbe79c14c25</t>
+          <t>32978baaf4964cea</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -19906,13 +19906,13 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.359712</v>
       </c>
       <c r="O68" s="28" t="n">
         <v>0.456135</v>
@@ -19921,7 +19921,7 @@
         <v>0.2</v>
       </c>
       <c r="Q68" s="28" t="n">
-        <v>0.08576499999999999</v>
+        <v>0.09642299999999999</v>
       </c>
       <c r="R68" s="26" t="n">
         <v>0</v>
@@ -19950,7 +19950,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3700 (atc-arg2-ste-casm-2026-08-02-ste).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-arg2-ste-casm-2026-08-02-ste).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:26.834968Z</t>
+          <t>2026-08-02T09:54:39.685627Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20079,13 +20079,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.359712</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>
@@ -20119,12 +20119,12 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>207400d6575545fb</t>
+          <t>fe773d8e01ee40b4</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:26.808979Z</t>
+          <t>2026-08-02T09:54:39.703999Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20382,12 +20382,12 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>e88f0fa338274204</t>
+          <t>214918333bf349d8</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:27.355220Z</t>
+          <t>2026-08-02T09:54:40.221601Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -20645,12 +20645,12 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>bc81abee15784afc</t>
+          <t>0514f21bad6c4359</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -20695,13 +20695,13 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.380228</v>
       </c>
       <c r="O71" s="28" t="n">
         <v>0.456135</v>
@@ -20710,7 +20710,7 @@
         <v>0.2</v>
       </c>
       <c r="Q71" s="28" t="n">
-        <v>0.08576499999999999</v>
+        <v>0.075907</v>
       </c>
       <c r="R71" s="26" t="n">
         <v>0</v>
@@ -20739,7 +20739,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3700 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3800 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -20858,7 +20858,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:27.689892Z</t>
+          <t>2026-08-02T09:54:40.577882Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -20868,13 +20868,13 @@
       </c>
       <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.380228</v>
       </c>
       <c r="BN71" s="28" t="n"/>
       <c r="BO71" s="28" t="n"/>
@@ -20908,12 +20908,12 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>e02d784cb60042dd</t>
+          <t>53303e6447614a38</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:28.471107Z</t>
+          <t>2026-08-02T09:54:41.230040Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21171,12 +21171,12 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>deda227db4bb477d</t>
+          <t>cf787d0ea17d4fda</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:29.617042Z</t>
+          <t>2026-08-02T09:54:42.369305Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21434,12 +21434,12 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>c3143d1900784cca</t>
+          <t>66f4086e58d94b33</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:29.597576Z</t>
+          <t>2026-08-02T09:54:42.293556Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -21697,12 +21697,12 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>c958fb5136a7467f</t>
+          <t>1eb95676931b4bb4</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -21910,7 +21910,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:30.643343Z</t>
+          <t>2026-08-02T09:54:43.328406Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -21960,12 +21960,12 @@
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>d2792e8a333f49ec</t>
+          <t>be8666391a204f27</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:31.136989Z</t>
+          <t>2026-08-02T09:54:43.918322Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22223,12 +22223,12 @@
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>b0810b50b6a443b6</t>
+          <t>323d75a83a4346a0</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
@@ -22273,13 +22273,13 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.330033</v>
       </c>
       <c r="O77" s="28" t="n">
         <v>0.406677</v>
@@ -22288,7 +22288,7 @@
         <v>0.19</v>
       </c>
       <c r="Q77" s="28" t="n">
-        <v>0.066541</v>
+        <v>0.076644</v>
       </c>
       <c r="R77" s="26" t="n">
         <v>0</v>
@@ -22317,7 +22317,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3400 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
+          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:31.689990Z</t>
+          <t>2026-08-02T09:54:44.442243Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22446,13 +22446,13 @@
       </c>
       <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.330033</v>
       </c>
       <c r="BN77" s="28" t="n"/>
       <c r="BO77" s="28" t="n"/>
@@ -22486,12 +22486,12 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>f9f5fabcb4d74d39</t>
+          <t>fe3d83605aa040de</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -22536,13 +22536,13 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.44843</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.690402</v>
       </c>
       <c r="O78" s="28" t="n">
         <v>0.515227</v>
@@ -22551,7 +22551,7 @@
         <v>0.04</v>
       </c>
       <c r="Q78" s="28" t="n">
-        <v>-0.184473</v>
+        <v>-0.175175</v>
       </c>
       <c r="R78" s="26" t="n">
         <v>0</v>
@@ -22580,7 +22580,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.7000 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
+          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.6900 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:33.477773Z</t>
+          <t>2026-08-02T09:54:46.103062Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -22709,13 +22709,13 @@
       </c>
       <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>-233</v>
+        <v>-223</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.44843</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.690402</v>
       </c>
       <c r="BN78" s="28" t="n"/>
       <c r="BO78" s="28" t="n"/>
@@ -22749,12 +22749,12 @@
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>d6fcf7d09f564659</t>
+          <t>78b9767e6a8c4d56</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
@@ -22799,13 +22799,13 @@
         </is>
       </c>
       <c r="L79" s="26" t="n">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="M79" s="27" t="n">
-        <v>2.86</v>
+        <v>3.23</v>
       </c>
       <c r="N79" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.309598</v>
       </c>
       <c r="O79" s="28" t="n">
         <v>0.575359</v>
@@ -22814,7 +22814,7 @@
         <v>0.04</v>
       </c>
       <c r="Q79" s="28" t="n">
-        <v>0.225709</v>
+        <v>0.265761</v>
       </c>
       <c r="R79" s="26" t="n">
         <v>100</v>
@@ -22843,7 +22843,7 @@
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3500 (atc-clbf-fey-ata-2026-08-02-fey).</t>
+          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3100 (atc-clbf-fey-ata-2026-08-02-fey).</t>
         </is>
       </c>
       <c r="AF79" s="31" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:33.464341Z</t>
+          <t>2026-08-02T09:54:46.127217Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -22972,13 +22972,13 @@
       </c>
       <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="BL79" s="27" t="n">
-        <v>2.86</v>
+        <v>3.23</v>
       </c>
       <c r="BM79" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.309598</v>
       </c>
       <c r="BN79" s="28" t="n"/>
       <c r="BO79" s="28" t="n"/>
@@ -23012,12 +23012,12 @@
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>e6c66f97d0f141ee</t>
+          <t>e9005480f16343a0</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:33.982808Z</t>
+          <t>2026-08-02T09:54:46.614326Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -23275,12 +23275,12 @@
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>0285ccf74ed94091</t>
+          <t>3478a0537c224584</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -23325,13 +23325,13 @@
         </is>
       </c>
       <c r="L81" s="26" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="M81" s="27" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="N81" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.480769</v>
       </c>
       <c r="O81" s="28" t="n">
         <v>0.395592</v>
@@ -23340,7 +23340,7 @@
         <v>0.04</v>
       </c>
       <c r="Q81" s="28" t="n">
-        <v>-0.073892</v>
+        <v>-0.085177</v>
       </c>
       <c r="R81" s="26" t="n">
         <v>0</v>
@@ -23369,7 +23369,7 @@
       <c r="AD81" s="24" t="n"/>
       <c r="AE81" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.40 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-clbf-sun-wre-2026-08-02-sun).</t>
+          <t>Poisson-DC rates 1.40 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4800 (atc-clbf-sun-wre-2026-08-02-sun).</t>
         </is>
       </c>
       <c r="AF81" s="31" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:34.058807Z</t>
+          <t>2026-08-02T09:54:46.711603Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -23498,13 +23498,13 @@
       </c>
       <c r="BJ81" s="25" t="n"/>
       <c r="BK81" s="26" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="BL81" s="27" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BM81" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.480769</v>
       </c>
       <c r="BN81" s="28" t="n"/>
       <c r="BO81" s="28" t="n"/>
@@ -23538,12 +23538,12 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>5a11720a728f4ecd</t>
+          <t>318d5c1521724b59</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:16:59.190075Z</t>
+          <t>2026-08-02T09:57:54.726368Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -23588,13 +23588,13 @@
         </is>
       </c>
       <c r="L82" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="M82" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="N82" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="O82" s="28" t="n">
         <v>0.482992</v>
@@ -23603,7 +23603,7 @@
         <v>0.04</v>
       </c>
       <c r="Q82" s="28" t="n">
-        <v>-0.087823</v>
+        <v>-0.09684</v>
       </c>
       <c r="R82" s="26" t="n">
         <v>0</v>
@@ -23632,7 +23632,7 @@
       <c r="AD82" s="24" t="n"/>
       <c r="AE82" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.69 (home) / 1.17 (away) from EWMA attack/defense strengths. Executable ask 0.5700 (atc-clbf-lfc-lee-2026-08-02-lfc).</t>
+          <t>Poisson-DC rates 1.69 (home) / 1.17 (away) from EWMA attack/defense strengths. Executable ask 0.5800 (atc-clbf-lfc-lee-2026-08-02-lfc).</t>
         </is>
       </c>
       <c r="AF82" s="31" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:13:34.558949Z</t>
+          <t>2026-08-02T09:54:47.218966Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -23761,13 +23761,13 @@
       </c>
       <c r="BJ82" s="25" t="n"/>
       <c r="BK82" s="26" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="BL82" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.724638</v>
       </c>
       <c r="BM82" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.579832</v>
       </c>
       <c r="BN82" s="28" t="n"/>
       <c r="BO82" s="28" t="n"/>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO82" headerRowCount="1">
-  <autoFilter ref="A1:CO82"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP82" headerRowCount="1">
+  <autoFilter ref="A1:CP82"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO82"/>
+  <dimension ref="A1:CP82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1855,6 +1862,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2132,6 +2140,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2413,6 +2422,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2690,6 +2700,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2967,6 +2978,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3244,6 +3256,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3521,6 +3534,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3798,6 +3812,7 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4075,6 +4090,7 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4352,6 +4368,7 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4629,6 +4646,7 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4906,6 +4924,7 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5183,6 +5202,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5460,6 +5480,7 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5737,6 +5758,7 @@
       <c r="CM16" s="24" t="n"/>
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6014,6 +6036,7 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6291,6 +6314,7 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6568,6 +6592,7 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6845,6 +6870,7 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7122,6 +7148,7 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7399,6 +7426,7 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7676,6 +7704,7 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -7953,6 +7982,7 @@
       <c r="CM24" s="24" t="n"/>
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8230,6 +8260,7 @@
       <c r="CM25" s="24" t="n"/>
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8507,6 +8538,7 @@
       <c r="CM26" s="24" t="n"/>
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8784,6 +8816,7 @@
       <c r="CM27" s="24" t="n"/>
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9061,6 +9094,7 @@
       <c r="CM28" s="24" t="n"/>
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9338,6 +9372,7 @@
       <c r="CM29" s="24" t="n"/>
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9615,6 +9650,7 @@
       <c r="CM30" s="24" t="n"/>
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -9892,6 +9928,7 @@
       <c r="CM31" s="24" t="n"/>
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10169,6 +10206,7 @@
       <c r="CM32" s="24" t="n"/>
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10446,6 +10484,7 @@
       <c r="CM33" s="24" t="n"/>
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10723,6 +10762,7 @@
       <c r="CM34" s="24" t="n"/>
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11000,6 +11040,7 @@
       <c r="CM35" s="24" t="n"/>
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11277,6 +11318,7 @@
       <c r="CM36" s="24" t="n"/>
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11554,6 +11596,7 @@
       <c r="CM37" s="24" t="n"/>
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -11835,6 +11878,7 @@
       <c r="CM38" s="24" t="n"/>
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
@@ -12116,6 +12160,7 @@
       <c r="CM39" s="24" t="n"/>
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
@@ -12397,6 +12442,7 @@
       <c r="CM40" s="24" t="n"/>
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
@@ -12678,6 +12724,7 @@
       <c r="CM41" s="24" t="n"/>
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
@@ -12955,6 +13002,7 @@
       <c r="CM42" s="24" t="n"/>
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
@@ -13232,6 +13280,7 @@
       <c r="CM43" s="24" t="n"/>
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
@@ -13509,6 +13558,7 @@
       <c r="CM44" s="24" t="n"/>
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
@@ -13786,6 +13836,7 @@
       <c r="CM45" s="24" t="n"/>
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
@@ -14063,6 +14114,7 @@
       <c r="CM46" s="24" t="n"/>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
@@ -14340,6 +14392,7 @@
       <c r="CM47" s="24" t="n"/>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
@@ -14617,6 +14670,7 @@
       <c r="CM48" s="24" t="n"/>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
@@ -14898,6 +14952,7 @@
       <c r="CM49" s="24" t="n"/>
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -15179,6 +15234,7 @@
       <c r="CM50" s="24" t="n"/>
       <c r="CN50" s="24" t="n"/>
       <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
@@ -15460,6 +15516,7 @@
       <c r="CM51" s="24" t="n"/>
       <c r="CN51" s="24" t="n"/>
       <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
@@ -15741,6 +15798,7 @@
       <c r="CM52" s="24" t="n"/>
       <c r="CN52" s="24" t="n"/>
       <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
@@ -16022,6 +16080,7 @@
       <c r="CM53" s="24" t="n"/>
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
@@ -16303,6 +16362,7 @@
       <c r="CM54" s="24" t="n"/>
       <c r="CN54" s="24" t="n"/>
       <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
@@ -16584,6 +16644,7 @@
       <c r="CM55" s="24" t="n"/>
       <c r="CN55" s="24" t="n"/>
       <c r="CO55" s="24" t="n"/>
+      <c r="CP55" s="24" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
@@ -16861,6 +16922,7 @@
       <c r="CM56" s="24" t="n"/>
       <c r="CN56" s="24" t="n"/>
       <c r="CO56" s="24" t="n"/>
+      <c r="CP56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
@@ -17138,6 +17200,7 @@
       <c r="CM57" s="24" t="n"/>
       <c r="CN57" s="24" t="n"/>
       <c r="CO57" s="24" t="n"/>
+      <c r="CP57" s="24" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
@@ -17415,6 +17478,7 @@
       <c r="CM58" s="24" t="n"/>
       <c r="CN58" s="24" t="n"/>
       <c r="CO58" s="24" t="n"/>
+      <c r="CP58" s="24" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
@@ -17692,6 +17756,7 @@
       <c r="CM59" s="24" t="n"/>
       <c r="CN59" s="24" t="n"/>
       <c r="CO59" s="24" t="n"/>
+      <c r="CP59" s="24" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
@@ -17969,6 +18034,7 @@
       <c r="CM60" s="24" t="n"/>
       <c r="CN60" s="24" t="n"/>
       <c r="CO60" s="24" t="n"/>
+      <c r="CP60" s="24" t="n"/>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
@@ -18246,6 +18312,7 @@
       <c r="CM61" s="24" t="n"/>
       <c r="CN61" s="24" t="n"/>
       <c r="CO61" s="24" t="n"/>
+      <c r="CP61" s="24" t="n"/>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
@@ -18523,6 +18590,7 @@
       <c r="CM62" s="24" t="n"/>
       <c r="CN62" s="24" t="n"/>
       <c r="CO62" s="24" t="n"/>
+      <c r="CP62" s="24" t="n"/>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
@@ -18800,26 +18868,27 @@
       <c r="CM63" s="24" t="n"/>
       <c r="CN63" s="24" t="n"/>
       <c r="CO63" s="24" t="n"/>
+      <c r="CP63" s="24" t="n"/>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>2a34a934fddc4d04</t>
+          <t>4d895a66fde74244</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T12:28:25.454250Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:30Z</t>
+          <t>2026-08-02T12:30Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401841470</t>
+          <t>401886552</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -18829,12 +18898,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -18844,7 +18913,7 @@
       </c>
       <c r="I64" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J64" s="25" t="n"/>
@@ -18854,25 +18923,25 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>233</v>
+        <v>-194</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>3.33</v>
+        <v>1.515464</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.659864</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.515227</v>
       </c>
       <c r="P64" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0.155835</v>
+        <v>-0.144637</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S64" s="29" t="n">
         <v>1</v>
@@ -18898,7 +18967,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-lpa-ald-gim-2026-08-02-ald).</t>
+          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.6600 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -18934,37 +19003,37 @@
       </c>
       <c r="AO64" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>FC Volendam</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -18977,7 +19046,7 @@
       <c r="AY64" s="24" t="n"/>
       <c r="AZ64" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA64" s="24" t="inlineStr">
@@ -19017,7 +19086,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:37.993984Z</t>
+          <t>2026-08-02T12:25:27.623402Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19027,13 +19096,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>233</v>
+        <v>-194</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>3.33</v>
+        <v>1.515464</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.659864</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -19063,26 +19132,27 @@
       <c r="CM64" s="24" t="n"/>
       <c r="CN64" s="24" t="n"/>
       <c r="CO64" s="24" t="n"/>
+      <c r="CP64" s="24" t="n"/>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>1b408477fd7d412b</t>
+          <t>b93cfe1d302c48e3</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T12:28:25.454250Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:00Z</t>
+          <t>2026-08-02T13:00Z</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>401841473</t>
+          <t>401886551</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -19092,12 +19162,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Feyenoord Rotterdam</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -19117,28 +19187,28 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.25</v>
+        <v>0.340136</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.398039</v>
+        <v>0.575359</v>
       </c>
       <c r="P65" s="28" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>0.148039</v>
+        <v>0.235223</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="S65" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
@@ -19161,7 +19231,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2500 (atc-lpa-new-boc-2026-08-02-new).</t>
+          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3400 (atc-clbf-fey-ata-2026-08-02-fey).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -19179,7 +19249,7 @@
       <c r="AJ65" s="31" t="n"/>
       <c r="AK65" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL65" s="26" t="n">
@@ -19187,47 +19257,47 @@
       </c>
       <c r="AM65" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN65" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO65" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Feyenoord Rotterdam</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Feyenoord Rotterdam</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Feyenoord Rotterdam</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -19240,7 +19310,7 @@
       <c r="AY65" s="24" t="n"/>
       <c r="AZ65" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA65" s="24" t="inlineStr">
@@ -19280,7 +19350,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:38.035675Z</t>
+          <t>2026-08-02T12:25:27.610137Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19290,13 +19360,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.25</v>
+        <v>0.340136</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -19326,26 +19396,27 @@
       <c r="CM65" s="24" t="n"/>
       <c r="CN65" s="24" t="n"/>
       <c r="CO65" s="24" t="n"/>
+      <c r="CP65" s="24" t="n"/>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>b3cc0a09be144952</t>
+          <t>0771f321dae74b18</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T22:15Z</t>
+          <t>2026-08-02T17:30Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401841476</t>
+          <t>401841470</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -19355,12 +19426,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -19380,25 +19451,25 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>2.08</v>
+        <v>3.33</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.3003</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.456135</v>
       </c>
       <c r="P66" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>0.055147</v>
+        <v>0.155835</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1</v>
@@ -19424,7 +19495,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4800 (atc-lpa-riv-ros-2026-08-02-riv).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-lpa-ald-gim-2026-08-02-ald).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -19442,7 +19513,7 @@
       <c r="AJ66" s="31" t="n"/>
       <c r="AK66" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL66" s="26" t="n">
@@ -19450,47 +19521,47 @@
       </c>
       <c r="AM66" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN66" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO66" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -19503,7 +19574,7 @@
       <c r="AY66" s="24" t="n"/>
       <c r="AZ66" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA66" s="24" t="inlineStr">
@@ -19543,7 +19614,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:38.550577Z</t>
+          <t>2026-08-02T13:02:42.194950Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19553,13 +19624,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>2.08</v>
+        <v>3.33</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.3003</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -19589,26 +19660,27 @@
       <c r="CM66" s="24" t="n"/>
       <c r="CN66" s="24" t="n"/>
       <c r="CO66" s="24" t="n"/>
+      <c r="CP66" s="24" t="n"/>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>e8d622bf760b47cf</t>
+          <t>56ce13751a194ba0</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T20:00Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401844015</t>
+          <t>401841473</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -19618,12 +19690,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -19643,25 +19715,25 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.229885</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.398039</v>
       </c>
       <c r="P67" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>0.005685</v>
+        <v>0.168154</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S67" s="29" t="n">
         <v>1</v>
@@ -19687,7 +19759,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-arg2-cjh-caa-2026-08-01-cjh).</t>
+          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2300 (atc-lpa-new-boc-2026-08-02-new).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -19705,7 +19777,7 @@
       <c r="AJ67" s="31" t="n"/>
       <c r="AK67" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL67" s="26" t="n">
@@ -19713,47 +19785,47 @@
       </c>
       <c r="AM67" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN67" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO67" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -19766,7 +19838,7 @@
       <c r="AY67" s="24" t="n"/>
       <c r="AZ67" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA67" s="24" t="inlineStr">
@@ -19806,7 +19878,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:39.105773Z</t>
+          <t>2026-08-02T13:02:42.189291Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19816,13 +19888,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.229885</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -19852,26 +19924,27 @@
       <c r="CM67" s="24" t="n"/>
       <c r="CN67" s="24" t="n"/>
       <c r="CO67" s="24" t="n"/>
+      <c r="CP67" s="24" t="n"/>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>32978baaf4964cea</t>
+          <t>707cd2cca2c34225</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T22:15Z</t>
         </is>
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>401844019</t>
+          <t>401841476</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -19881,12 +19954,12 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -19906,22 +19979,22 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.469484</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.5359159999999999</v>
       </c>
       <c r="P68" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q68" s="28" t="n">
-        <v>0.09642299999999999</v>
+        <v>0.066432</v>
       </c>
       <c r="R68" s="26" t="n">
         <v>0</v>
@@ -19950,7 +20023,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-arg2-ste-casm-2026-08-02-ste).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-lpa-riv-ros-2026-08-02-riv).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -19968,7 +20041,7 @@
       <c r="AJ68" s="31" t="n"/>
       <c r="AK68" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL68" s="26" t="n">
@@ -19976,47 +20049,47 @@
       </c>
       <c r="AM68" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN68" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO68" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP68" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AQ68" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AR68" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AS68" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AT68" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AU68" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AV68" s="24" t="n"/>
@@ -20029,7 +20102,7 @@
       <c r="AY68" s="24" t="n"/>
       <c r="AZ68" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA68" s="24" t="inlineStr">
@@ -20069,7 +20142,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:39.685627Z</t>
+          <t>2026-08-02T13:02:42.667349Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20079,13 +20152,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.469484</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>
@@ -20115,26 +20188,27 @@
       <c r="CM68" s="24" t="n"/>
       <c r="CN68" s="24" t="n"/>
       <c r="CO68" s="24" t="n"/>
+      <c r="CP68" s="24" t="n"/>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>fe773d8e01ee40b4</t>
+          <t>01019c2bfb1647f2</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:30Z</t>
+          <t>2026-08-02T18:00Z</t>
         </is>
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>401844012</t>
+          <t>401844015</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -20144,12 +20218,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -20169,13 +20243,13 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M69" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="O69" s="28" t="n">
         <v>0.456135</v>
@@ -20184,7 +20258,7 @@
         <v>0.2</v>
       </c>
       <c r="Q69" s="28" t="n">
-        <v>-0.004694</v>
+        <v>0.005685</v>
       </c>
       <c r="R69" s="26" t="n">
         <v>0</v>
@@ -20213,7 +20287,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-cat-gyt-2026-08-02-cat).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-arg2-cjh-caa-2026-08-01-cjh).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -20249,37 +20323,37 @@
       </c>
       <c r="AO69" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -20292,7 +20366,7 @@
       <c r="AY69" s="24" t="n"/>
       <c r="AZ69" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA69" s="24" t="inlineStr">
@@ -20332,7 +20406,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:39.703999Z</t>
+          <t>2026-08-02T13:02:43.309952Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20342,13 +20416,13 @@
       </c>
       <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BL69" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="BN69" s="28" t="n"/>
       <c r="BO69" s="28" t="n"/>
@@ -20378,26 +20452,27 @@
       <c r="CM69" s="24" t="n"/>
       <c r="CN69" s="24" t="n"/>
       <c r="CO69" s="24" t="n"/>
+      <c r="CP69" s="24" t="n"/>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>214918333bf349d8</t>
+          <t>10cdf787a7554ce4</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:00Z</t>
+          <t>2026-08-02T18:00Z</t>
         </is>
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>401844026</t>
+          <t>401844019</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -20407,12 +20482,12 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G70" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr">
@@ -20432,13 +20507,13 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>-104</v>
+        <v>178</v>
       </c>
       <c r="M70" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.78</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.359712</v>
       </c>
       <c r="O70" s="28" t="n">
         <v>0.456135</v>
@@ -20447,7 +20522,7 @@
         <v>0.2</v>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>-0.053669</v>
+        <v>0.09642299999999999</v>
       </c>
       <c r="R70" s="26" t="n">
         <v>0</v>
@@ -20476,7 +20551,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-arg2-dma-abo-2026-08-02-dma).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-arg2-ste-casm-2026-08-02-ste).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -20494,7 +20569,7 @@
       <c r="AJ70" s="31" t="n"/>
       <c r="AK70" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL70" s="26" t="n">
@@ -20502,47 +20577,47 @@
       </c>
       <c r="AM70" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN70" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO70" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP70" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="AQ70" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="AR70" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="AS70" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="AT70" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="AU70" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="AV70" s="24" t="n"/>
@@ -20555,7 +20630,7 @@
       <c r="AY70" s="24" t="n"/>
       <c r="AZ70" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA70" s="24" t="inlineStr">
@@ -20595,7 +20670,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:40.221601Z</t>
+          <t>2026-08-02T13:02:43.878798Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -20605,13 +20680,13 @@
       </c>
       <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>-104</v>
+        <v>178</v>
       </c>
       <c r="BL70" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.78</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.359712</v>
       </c>
       <c r="BN70" s="28" t="n"/>
       <c r="BO70" s="28" t="n"/>
@@ -20641,26 +20716,27 @@
       <c r="CM70" s="24" t="n"/>
       <c r="CN70" s="24" t="n"/>
       <c r="CO70" s="24" t="n"/>
+      <c r="CP70" s="24" t="n"/>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>0514f21bad6c4359</t>
+          <t>245e3f4789a5452a</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:30Z</t>
+          <t>2026-08-02T18:30Z</t>
         </is>
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>401844014</t>
+          <t>401844012</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
@@ -20670,12 +20746,12 @@
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -20695,13 +20771,13 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.460829</v>
       </c>
       <c r="O71" s="28" t="n">
         <v>0.456135</v>
@@ -20710,7 +20786,7 @@
         <v>0.2</v>
       </c>
       <c r="Q71" s="28" t="n">
-        <v>0.075907</v>
+        <v>-0.004694</v>
       </c>
       <c r="R71" s="26" t="n">
         <v>0</v>
@@ -20739,7 +20815,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3800 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-cat-gyt-2026-08-02-cat).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -20775,37 +20851,37 @@
       </c>
       <c r="AO71" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP71" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AQ71" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AR71" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AS71" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="AT71" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="AU71" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="AV71" s="24" t="n"/>
@@ -20818,7 +20894,7 @@
       <c r="AY71" s="24" t="n"/>
       <c r="AZ71" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA71" s="24" t="inlineStr">
@@ -20858,7 +20934,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:40.577882Z</t>
+          <t>2026-08-02T13:02:43.831258Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -20868,13 +20944,13 @@
       </c>
       <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.460829</v>
       </c>
       <c r="BN71" s="28" t="n"/>
       <c r="BO71" s="28" t="n"/>
@@ -20904,26 +20980,27 @@
       <c r="CM71" s="24" t="n"/>
       <c r="CN71" s="24" t="n"/>
       <c r="CO71" s="24" t="n"/>
+      <c r="CP71" s="24" t="n"/>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>53303e6447614a38</t>
+          <t>f61ec0eaa3ed4ea1</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T01:00Z</t>
+          <t>2026-08-02T19:00Z</t>
         </is>
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>401877966</t>
+          <t>401844026</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
@@ -20933,12 +21010,12 @@
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
@@ -20958,13 +21035,13 @@
         </is>
       </c>
       <c r="L72" s="26" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="M72" s="27" t="n">
-        <v>2.17</v>
+        <v>1.961538</v>
       </c>
       <c r="N72" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.509804</v>
       </c>
       <c r="O72" s="28" t="n">
         <v>0.456135</v>
@@ -20973,7 +21050,7 @@
         <v>0.2</v>
       </c>
       <c r="Q72" s="28" t="n">
-        <v>-0.004694</v>
+        <v>-0.053669</v>
       </c>
       <c r="R72" s="26" t="n">
         <v>0</v>
@@ -21002,7 +21079,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lco-san-onc-2026-08-02-san).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-arg2-dma-abo-2026-08-02-dma).</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -21038,37 +21115,37 @@
       </c>
       <c r="AO72" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP72" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="AQ72" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="AR72" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="AS72" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="AT72" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="AU72" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="AV72" s="24" t="n"/>
@@ -21081,7 +21158,7 @@
       <c r="AY72" s="24" t="n"/>
       <c r="AZ72" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA72" s="24" t="inlineStr">
@@ -21121,7 +21198,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:41.230040Z</t>
+          <t>2026-08-02T13:02:44.367919Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21131,13 +21208,13 @@
       </c>
       <c r="BJ72" s="25" t="n"/>
       <c r="BK72" s="26" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="BL72" s="27" t="n">
-        <v>2.17</v>
+        <v>1.961538</v>
       </c>
       <c r="BM72" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.509804</v>
       </c>
       <c r="BN72" s="28" t="n"/>
       <c r="BO72" s="28" t="n"/>
@@ -21167,26 +21244,27 @@
       <c r="CM72" s="24" t="n"/>
       <c r="CN72" s="24" t="n"/>
       <c r="CO72" s="24" t="n"/>
+      <c r="CP72" s="24" t="n"/>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>cf787d0ea17d4fda</t>
+          <t>5109ef785f354463</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:00Z</t>
+          <t>2026-08-02T19:30Z</t>
         </is>
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>401850609</t>
+          <t>401844014</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
@@ -21196,12 +21274,12 @@
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -21221,22 +21299,22 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.4</v>
+        <v>0.390625</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.456135</v>
       </c>
       <c r="P73" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q73" s="28" t="n">
-        <v>0.135916</v>
+        <v>0.06551</v>
       </c>
       <c r="R73" s="26" t="n">
         <v>0</v>
@@ -21265,7 +21343,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4000 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -21283,7 +21361,7 @@
       <c r="AJ73" s="31" t="n"/>
       <c r="AK73" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL73" s="26" t="n">
@@ -21291,47 +21369,47 @@
       </c>
       <c r="AM73" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN73" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO73" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP73" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="AQ73" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="AR73" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="AS73" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="AT73" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="AU73" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="AV73" s="24" t="n"/>
@@ -21344,7 +21422,7 @@
       <c r="AY73" s="24" t="n"/>
       <c r="AZ73" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA73" s="24" t="inlineStr">
@@ -21384,7 +21462,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:42.369305Z</t>
+          <t>2026-08-02T13:02:44.924772Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21394,13 +21472,13 @@
       </c>
       <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.4</v>
+        <v>0.390625</v>
       </c>
       <c r="BN73" s="28" t="n"/>
       <c r="BO73" s="28" t="n"/>
@@ -21430,26 +21508,27 @@
       <c r="CM73" s="24" t="n"/>
       <c r="CN73" s="24" t="n"/>
       <c r="CO73" s="24" t="n"/>
+      <c r="CP73" s="24" t="n"/>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>66f4086e58d94b33</t>
+          <t>d38a7a67a080456e</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:30Z</t>
+          <t>2026-08-03T01:00Z</t>
         </is>
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>401850607</t>
+          <t>401877966</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
@@ -21459,12 +21538,12 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -21484,22 +21563,22 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-170</v>
+        <v>117</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.17</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.460829</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.414794</v>
+        <v>0.456135</v>
       </c>
       <c r="P74" s="28" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="Q74" s="28" t="n">
-        <v>-0.214836</v>
+        <v>-0.004694</v>
       </c>
       <c r="R74" s="26" t="n">
         <v>0</v>
@@ -21528,7 +21607,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-pdc-unc-hua-2026-08-02-unc).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lco-san-onc-2026-08-02-san).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -21564,37 +21643,37 @@
       </c>
       <c r="AO74" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -21607,7 +21686,7 @@
       <c r="AY74" s="24" t="n"/>
       <c r="AZ74" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA74" s="24" t="inlineStr">
@@ -21647,7 +21726,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:42.293556Z</t>
+          <t>2026-08-02T13:02:45.478968Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -21657,13 +21736,13 @@
       </c>
       <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>-170</v>
+        <v>117</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.17</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.460829</v>
       </c>
       <c r="BN74" s="28" t="n"/>
       <c r="BO74" s="28" t="n"/>
@@ -21693,26 +21772,27 @@
       <c r="CM74" s="24" t="n"/>
       <c r="CN74" s="24" t="n"/>
       <c r="CO74" s="24" t="n"/>
+      <c r="CP74" s="24" t="n"/>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>1eb95676931b4bb4</t>
+          <t>8693acfb41e243fd</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:00Z</t>
+          <t>2026-08-02T19:00Z</t>
         </is>
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>401872734</t>
+          <t>401850609</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
@@ -21722,12 +21802,12 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr">
@@ -21747,13 +21827,13 @@
         </is>
       </c>
       <c r="L75" s="26" t="n">
-        <v>-127</v>
+        <v>150</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.5</v>
       </c>
       <c r="N75" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.4</v>
       </c>
       <c r="O75" s="28" t="n">
         <v>0.5359159999999999</v>
@@ -21762,7 +21842,7 @@
         <v>0.2</v>
       </c>
       <c r="Q75" s="28" t="n">
-        <v>-0.023555</v>
+        <v>0.135916</v>
       </c>
       <c r="R75" s="26" t="n">
         <v>0</v>
@@ -21791,7 +21871,7 @@
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-uru1-rcm-bri-2026-08-02-rcm).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4000 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
         </is>
       </c>
       <c r="AF75" s="31" t="inlineStr">
@@ -21809,7 +21889,7 @@
       <c r="AJ75" s="31" t="n"/>
       <c r="AK75" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL75" s="26" t="n">
@@ -21817,47 +21897,47 @@
       </c>
       <c r="AM75" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN75" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO75" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP75" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="AQ75" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="AR75" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="AS75" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="AT75" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="AU75" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="AV75" s="24" t="n"/>
@@ -21870,7 +21950,7 @@
       <c r="AY75" s="24" t="n"/>
       <c r="AZ75" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA75" s="24" t="inlineStr">
@@ -21910,7 +21990,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:43.328406Z</t>
+          <t>2026-08-02T13:02:46.605203Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -21920,13 +22000,13 @@
       </c>
       <c r="BJ75" s="25" t="n"/>
       <c r="BK75" s="26" t="n">
-        <v>-127</v>
+        <v>150</v>
       </c>
       <c r="BL75" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.5</v>
       </c>
       <c r="BM75" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.4</v>
       </c>
       <c r="BN75" s="28" t="n"/>
       <c r="BO75" s="28" t="n"/>
@@ -21956,26 +22036,27 @@
       <c r="CM75" s="24" t="n"/>
       <c r="CN75" s="24" t="n"/>
       <c r="CO75" s="24" t="n"/>
+      <c r="CP75" s="24" t="n"/>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>be8666391a204f27</t>
+          <t>fadf84ce72c64e10</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:30Z</t>
+          <t>2026-08-02T21:30Z</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>401859644</t>
+          <t>401850607</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
@@ -21985,12 +22066,12 @@
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
@@ -22010,22 +22091,22 @@
         </is>
       </c>
       <c r="L76" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="N76" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="O76" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.414794</v>
       </c>
       <c r="P76" s="28" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q76" s="28" t="n">
-        <v>-0.194215</v>
+        <v>-0.214836</v>
       </c>
       <c r="R76" s="26" t="n">
         <v>0</v>
@@ -22054,7 +22135,7 @@
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-ecu1-mac-gua-2026-08-02-mac).</t>
+          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-pdc-unc-hua-2026-08-02-unc).</t>
         </is>
       </c>
       <c r="AF76" s="31" t="inlineStr">
@@ -22090,37 +22171,37 @@
       </c>
       <c r="AO76" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP76" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="AQ76" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="AR76" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="AS76" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="AT76" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="AU76" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="AV76" s="24" t="n"/>
@@ -22133,7 +22214,7 @@
       <c r="AY76" s="24" t="n"/>
       <c r="AZ76" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA76" s="24" t="inlineStr">
@@ -22173,7 +22254,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:43.918322Z</t>
+          <t>2026-08-02T13:02:46.553813Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22183,13 +22264,13 @@
       </c>
       <c r="BJ76" s="25" t="n"/>
       <c r="BK76" s="26" t="n">
-        <v>-186</v>
+        <v>-170</v>
       </c>
       <c r="BL76" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.588235</v>
       </c>
       <c r="BM76" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.62963</v>
       </c>
       <c r="BN76" s="28" t="n"/>
       <c r="BO76" s="28" t="n"/>
@@ -22219,26 +22300,27 @@
       <c r="CM76" s="24" t="n"/>
       <c r="CN76" s="24" t="n"/>
       <c r="CO76" s="24" t="n"/>
+      <c r="CP76" s="24" t="n"/>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>323d75a83a4346a0</t>
+          <t>c263948c11c94638</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T23:10Z</t>
+          <t>2026-08-02T15:00Z</t>
         </is>
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>401859718</t>
+          <t>401872734</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
@@ -22248,12 +22330,12 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="G77" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr">
@@ -22263,7 +22345,7 @@
       </c>
       <c r="I77" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J77" s="25" t="n"/>
@@ -22273,22 +22355,22 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>203</v>
+        <v>-127</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>3.03</v>
+        <v>1.787402</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O77" s="28" t="n">
-        <v>0.406677</v>
+        <v>0.5359159999999999</v>
       </c>
       <c r="P77" s="28" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="Q77" s="28" t="n">
-        <v>0.076644</v>
+        <v>-0.023555</v>
       </c>
       <c r="R77" s="26" t="n">
         <v>0</v>
@@ -22317,7 +22399,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-uru1-rcm-bri-2026-08-02-rcm).</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -22353,37 +22435,37 @@
       </c>
       <c r="AO77" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP77" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="AQ77" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="AR77" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="AS77" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="AT77" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="AU77" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="AV77" s="24" t="n"/>
@@ -22396,7 +22478,7 @@
       <c r="AY77" s="24" t="n"/>
       <c r="AZ77" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA77" s="24" t="inlineStr">
@@ -22436,7 +22518,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:44.442243Z</t>
+          <t>2026-08-02T13:02:47.678863Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22446,13 +22528,13 @@
       </c>
       <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
-        <v>203</v>
+        <v>-127</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>3.03</v>
+        <v>1.787402</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN77" s="28" t="n"/>
       <c r="BO77" s="28" t="n"/>
@@ -22482,26 +22564,27 @@
       <c r="CM77" s="24" t="n"/>
       <c r="CN77" s="24" t="n"/>
       <c r="CO77" s="24" t="n"/>
+      <c r="CP77" s="24" t="n"/>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>fe3d83605aa040de</t>
+          <t>eb5c055fd013485c</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T12:30Z</t>
+          <t>2026-08-02T20:30Z</t>
         </is>
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>401886552</t>
+          <t>401859644</t>
         </is>
       </c>
       <c r="E78" s="24" t="inlineStr">
@@ -22511,12 +22594,12 @@
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G78" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr">
@@ -22526,7 +22609,7 @@
       </c>
       <c r="I78" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J78" s="25" t="n"/>
@@ -22536,22 +22619,22 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-223</v>
+        <v>-186</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.537634</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.65035</v>
       </c>
       <c r="O78" s="28" t="n">
-        <v>0.515227</v>
+        <v>0.456135</v>
       </c>
       <c r="P78" s="28" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="Q78" s="28" t="n">
-        <v>-0.175175</v>
+        <v>-0.194215</v>
       </c>
       <c r="R78" s="26" t="n">
         <v>0</v>
@@ -22580,7 +22663,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.6900 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-ecu1-mac-gua-2026-08-02-mac).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -22616,37 +22699,37 @@
       </c>
       <c r="AO78" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP78" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="AQ78" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="AR78" s="24" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="AS78" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="AT78" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="AU78" s="24" t="inlineStr">
         <is>
-          <t>FC Volendam</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="AV78" s="24" t="n"/>
@@ -22659,7 +22742,7 @@
       <c r="AY78" s="24" t="n"/>
       <c r="AZ78" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA78" s="24" t="inlineStr">
@@ -22699,7 +22782,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:46.103062Z</t>
+          <t>2026-08-02T13:02:48.243225Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -22709,13 +22792,13 @@
       </c>
       <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>-223</v>
+        <v>-186</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.537634</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.65035</v>
       </c>
       <c r="BN78" s="28" t="n"/>
       <c r="BO78" s="28" t="n"/>
@@ -22745,26 +22828,27 @@
       <c r="CM78" s="24" t="n"/>
       <c r="CN78" s="24" t="n"/>
       <c r="CO78" s="24" t="n"/>
+      <c r="CP78" s="24" t="n"/>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>78b9767e6a8c4d56</t>
+          <t>d0190a70cb46499d</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00Z</t>
+          <t>2026-08-02T23:10Z</t>
         </is>
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>401886551</t>
+          <t>401859718</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
@@ -22774,12 +22858,12 @@
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="G79" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr">
@@ -22789,7 +22873,7 @@
       </c>
       <c r="I79" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J79" s="25" t="n"/>
@@ -22799,28 +22883,28 @@
         </is>
       </c>
       <c r="L79" s="26" t="n">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="M79" s="27" t="n">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="N79" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.330033</v>
       </c>
       <c r="O79" s="28" t="n">
-        <v>0.575359</v>
+        <v>0.406677</v>
       </c>
       <c r="P79" s="28" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="Q79" s="28" t="n">
-        <v>0.265761</v>
+        <v>0.076644</v>
       </c>
       <c r="R79" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S79" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T79" s="24" t="inlineStr">
         <is>
@@ -22843,7 +22927,7 @@
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3100 (atc-clbf-fey-ata-2026-08-02-fey).</t>
+          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
         </is>
       </c>
       <c r="AF79" s="31" t="inlineStr">
@@ -22861,7 +22945,7 @@
       <c r="AJ79" s="31" t="n"/>
       <c r="AK79" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL79" s="26" t="n">
@@ -22869,47 +22953,47 @@
       </c>
       <c r="AM79" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN79" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO79" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP79" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="AQ79" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="AR79" s="24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="AS79" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="AT79" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="AU79" s="24" t="inlineStr">
         <is>
-          <t>Feyenoord Rotterdam</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="AV79" s="24" t="n"/>
@@ -22922,7 +23006,7 @@
       <c r="AY79" s="24" t="n"/>
       <c r="AZ79" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA79" s="24" t="inlineStr">
@@ -22962,7 +23046,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:46.127217Z</t>
+          <t>2026-08-02T13:02:48.734342Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -22972,13 +23056,13 @@
       </c>
       <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="BL79" s="27" t="n">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="BM79" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.330033</v>
       </c>
       <c r="BN79" s="28" t="n"/>
       <c r="BO79" s="28" t="n"/>
@@ -23008,16 +23092,17 @@
       <c r="CM79" s="24" t="n"/>
       <c r="CN79" s="24" t="n"/>
       <c r="CO79" s="24" t="n"/>
+      <c r="CP79" s="24" t="n"/>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>e9005480f16343a0</t>
+          <t>2d67de72f6ba48bd</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -23062,13 +23147,13 @@
         </is>
       </c>
       <c r="L80" s="26" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="M80" s="27" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="N80" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.390625</v>
       </c>
       <c r="O80" s="28" t="n">
         <v>0.395816</v>
@@ -23077,7 +23162,7 @@
         <v>0.2</v>
       </c>
       <c r="Q80" s="28" t="n">
-        <v>-0.01402</v>
+        <v>0.005191</v>
       </c>
       <c r="R80" s="26" t="n">
         <v>0</v>
@@ -23106,7 +23191,7 @@
       <c r="AD80" s="24" t="n"/>
       <c r="AE80" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.4100 (atc-clbf-tra-udi-2026-08-02-tra).</t>
+          <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-clbf-tra-udi-2026-08-02-tra).</t>
         </is>
       </c>
       <c r="AF80" s="31" t="inlineStr">
@@ -23142,7 +23227,7 @@
       </c>
       <c r="AO80" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP80" s="24" t="inlineStr">
@@ -23185,7 +23270,7 @@
       <c r="AY80" s="24" t="n"/>
       <c r="AZ80" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA80" s="24" t="inlineStr">
@@ -23225,7 +23310,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:46.614326Z</t>
+          <t>2026-08-02T13:02:50.866524Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -23235,13 +23320,13 @@
       </c>
       <c r="BJ80" s="25" t="n"/>
       <c r="BK80" s="26" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="BL80" s="27" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="BM80" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.390625</v>
       </c>
       <c r="BN80" s="28" t="n"/>
       <c r="BO80" s="28" t="n"/>
@@ -23271,16 +23356,17 @@
       <c r="CM80" s="24" t="n"/>
       <c r="CN80" s="24" t="n"/>
       <c r="CO80" s="24" t="n"/>
+      <c r="CP80" s="24" t="n"/>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>3478a0537c224584</t>
+          <t>c75bdecc61de4110</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -23405,7 +23491,7 @@
       </c>
       <c r="AO81" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP81" s="24" t="inlineStr">
@@ -23448,7 +23534,7 @@
       <c r="AY81" s="24" t="n"/>
       <c r="AZ81" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA81" s="24" t="inlineStr">
@@ -23488,7 +23574,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:46.711603Z</t>
+          <t>2026-08-02T13:02:50.974234Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -23534,16 +23620,17 @@
       <c r="CM81" s="24" t="n"/>
       <c r="CN81" s="24" t="n"/>
       <c r="CO81" s="24" t="n"/>
+      <c r="CP81" s="24" t="n"/>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>318d5c1521724b59</t>
+          <t>84b998c94a984f6b</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:57:54.726368Z</t>
+          <t>2026-08-02T13:05:47.245126Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -23668,7 +23755,7 @@
       </c>
       <c r="AO82" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP82" s="24" t="inlineStr">
@@ -23711,7 +23798,7 @@
       <c r="AY82" s="24" t="n"/>
       <c r="AZ82" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA82" s="24" t="inlineStr">
@@ -23751,7 +23838,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:54:47.218966Z</t>
+          <t>2026-08-02T13:02:51.442026Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -23797,6 +23884,7 @@
       <c r="CM82" s="24" t="n"/>
       <c r="CN82" s="24" t="n"/>
       <c r="CO82" s="24" t="n"/>
+      <c r="CP82" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -18953,18 +18953,32 @@
       </c>
       <c r="U64" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V64" s="24" t="n"/>
-      <c r="W64" s="26" t="n"/>
-      <c r="X64" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V64" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W64" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X64" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y64" s="25" t="n"/>
       <c r="Z64" s="26" t="n"/>
       <c r="AA64" s="28" t="n"/>
       <c r="AB64" s="28" t="n"/>
-      <c r="AC64" s="30" t="n"/>
-      <c r="AD64" s="24" t="n"/>
+      <c r="AC64" s="30" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="AD64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:27.869718Z</t>
+        </is>
+      </c>
       <c r="AE64" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 0.88 (home) / 1.54 (away) from EWMA attack/defense strengths. Executable ask 0.6600 (atc-clbf-fvco-aja-2026-08-02-aja).</t>
@@ -19217,18 +19231,32 @@
       </c>
       <c r="U65" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V65" s="24" t="n"/>
-      <c r="W65" s="26" t="n"/>
-      <c r="X65" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V65" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W65" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y65" s="25" t="n"/>
       <c r="Z65" s="26" t="n"/>
       <c r="AA65" s="28" t="n"/>
       <c r="AB65" s="28" t="n"/>
-      <c r="AC65" s="30" t="n"/>
-      <c r="AD65" s="24" t="n"/>
+      <c r="AC65" s="30" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AD65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:53:28.234366Z</t>
+        </is>
+      </c>
       <c r="AE65" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.92 (home) / 1.01 (away) from EWMA attack/defense strengths. Executable ask 0.3400 (atc-clbf-fey-ata-2026-08-02-fey).</t>
@@ -19401,7 +19429,7 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>0771f321dae74b18</t>
+          <t>c263948c11c94638</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
@@ -19411,12 +19439,12 @@
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:30Z</t>
+          <t>2026-08-02T15:00Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401841470</t>
+          <t>401872734</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -19426,12 +19454,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -19451,25 +19479,25 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>233</v>
+        <v>-127</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>3.33</v>
+        <v>1.787402</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.5359159999999999</v>
       </c>
       <c r="P66" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>0.155835</v>
+        <v>-0.023555</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1</v>
@@ -19495,7 +19523,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-lpa-ald-gim-2026-08-02-ald).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-uru1-rcm-bri-2026-08-02-rcm).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -19513,7 +19541,7 @@
       <c r="AJ66" s="31" t="n"/>
       <c r="AK66" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL66" s="26" t="n">
@@ -19521,47 +19549,47 @@
       </c>
       <c r="AM66" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN66" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO66" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Racing (Montevideo)</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -19614,7 +19642,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:42.194950Z</t>
+          <t>2026-08-02T13:02:47.678863Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19624,13 +19652,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>233</v>
+        <v>-127</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>3.33</v>
+        <v>1.787402</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.3003</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -19665,7 +19693,7 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>56ce13751a194ba0</t>
+          <t>2d67de72f6ba48bd</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
@@ -19675,12 +19703,12 @@
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:00Z</t>
+          <t>2026-08-02T14:30Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401841473</t>
+          <t>401898711</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -19690,12 +19718,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -19715,25 +19743,25 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>335</v>
+        <v>156</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>4.35</v>
+        <v>2.56</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.229885</v>
+        <v>0.390625</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.398039</v>
+        <v>0.395816</v>
       </c>
       <c r="P67" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>0.168154</v>
+        <v>0.005191</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S67" s="29" t="n">
         <v>1</v>
@@ -19759,7 +19787,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2300 (atc-lpa-new-boc-2026-08-02-new).</t>
+          <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-clbf-tra-udi-2026-08-02-tra).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -19777,7 +19805,7 @@
       <c r="AJ67" s="31" t="n"/>
       <c r="AK67" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL67" s="26" t="n">
@@ -19785,47 +19813,47 @@
       </c>
       <c r="AM67" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN67" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO67" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -19878,7 +19906,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:42.189291Z</t>
+          <t>2026-08-02T13:02:50.866524Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -19888,13 +19916,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>335</v>
+        <v>156</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>4.35</v>
+        <v>2.56</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.229885</v>
+        <v>0.390625</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -19929,22 +19957,22 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>707cd2cca2c34225</t>
+          <t>05052e7c469b4483</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T22:15Z</t>
+          <t>2026-08-02T17:30Z</t>
         </is>
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>401841476</t>
+          <t>401841470</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -19954,12 +19982,12 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -19979,25 +20007,25 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>113</v>
+        <v>233</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>2.13</v>
+        <v>3.33</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.3003</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.456135</v>
       </c>
       <c r="P68" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q68" s="28" t="n">
-        <v>0.066432</v>
+        <v>0.155835</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S68" s="29" t="n">
         <v>1</v>
@@ -20023,7 +20051,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-lpa-riv-ros-2026-08-02-riv).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3000 (atc-lpa-ald-gim-2026-08-02-ald).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -20064,32 +20092,32 @@
       </c>
       <c r="AP68" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AQ68" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AR68" s="24" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="AS68" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AT68" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AU68" s="24" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="AV68" s="24" t="n"/>
@@ -20142,7 +20170,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:42.667349Z</t>
+          <t>2026-08-02T15:46:29.596146Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20152,13 +20180,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>113</v>
+        <v>233</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>2.13</v>
+        <v>3.33</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.3003</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>
@@ -20188,27 +20216,31 @@
       <c r="CM68" s="24" t="n"/>
       <c r="CN68" s="24" t="n"/>
       <c r="CO68" s="24" t="n"/>
-      <c r="CP68" s="24" t="n"/>
+      <c r="CP68" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>01019c2bfb1647f2</t>
+          <t>215e684de33142bd</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T20:00Z</t>
         </is>
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>401844015</t>
+          <t>401841473</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -20218,12 +20250,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -20243,25 +20275,25 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="M69" s="27" t="n">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.229885</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.398039</v>
       </c>
       <c r="P69" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q69" s="28" t="n">
-        <v>0.005685</v>
+        <v>0.168154</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S69" s="29" t="n">
         <v>1</v>
@@ -20287,7 +20319,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-arg2-cjh-caa-2026-08-01-cjh).</t>
+          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2300 (atc-lpa-new-boc-2026-08-02-new).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -20305,7 +20337,7 @@
       <c r="AJ69" s="31" t="n"/>
       <c r="AK69" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL69" s="26" t="n">
@@ -20313,47 +20345,47 @@
       </c>
       <c r="AM69" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN69" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO69" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -20406,7 +20438,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:43.309952Z</t>
+          <t>2026-08-02T15:46:29.646850Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20416,13 +20448,13 @@
       </c>
       <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="BL69" s="27" t="n">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.229885</v>
       </c>
       <c r="BN69" s="28" t="n"/>
       <c r="BO69" s="28" t="n"/>
@@ -20452,27 +20484,31 @@
       <c r="CM69" s="24" t="n"/>
       <c r="CN69" s="24" t="n"/>
       <c r="CO69" s="24" t="n"/>
-      <c r="CP69" s="24" t="n"/>
+      <c r="CP69" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>10cdf787a7554ce4</t>
+          <t>f62501e8d0f24f4b</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00Z</t>
+          <t>2026-08-02T22:15Z</t>
         </is>
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>401844019</t>
+          <t>401841476</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -20482,12 +20518,12 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G70" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr">
@@ -20507,22 +20543,22 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="M70" s="27" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.469484</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.5359159999999999</v>
       </c>
       <c r="P70" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>0.09642299999999999</v>
+        <v>0.066432</v>
       </c>
       <c r="R70" s="26" t="n">
         <v>0</v>
@@ -20551,7 +20587,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3600 (atc-arg2-ste-casm-2026-08-02-ste).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4700 (atc-lpa-riv-ros-2026-08-02-riv).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -20592,32 +20628,32 @@
       </c>
       <c r="AP70" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AQ70" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AR70" s="24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="AS70" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AT70" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AU70" s="24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="AV70" s="24" t="n"/>
@@ -20670,7 +20706,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:43.878798Z</t>
+          <t>2026-08-02T15:46:30.158682Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -20680,13 +20716,13 @@
       </c>
       <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="BL70" s="27" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.469484</v>
       </c>
       <c r="BN70" s="28" t="n"/>
       <c r="BO70" s="28" t="n"/>
@@ -20716,27 +20752,31 @@
       <c r="CM70" s="24" t="n"/>
       <c r="CN70" s="24" t="n"/>
       <c r="CO70" s="24" t="n"/>
-      <c r="CP70" s="24" t="n"/>
+      <c r="CP70" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>245e3f4789a5452a</t>
+          <t>2465116f6fd34343</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:30Z</t>
+          <t>2026-08-02T18:00Z</t>
         </is>
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>401844012</t>
+          <t>401844015</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
@@ -20746,12 +20786,12 @@
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -20771,13 +20811,13 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="O71" s="28" t="n">
         <v>0.456135</v>
@@ -20786,7 +20826,7 @@
         <v>0.2</v>
       </c>
       <c r="Q71" s="28" t="n">
-        <v>-0.004694</v>
+        <v>0.005685</v>
       </c>
       <c r="R71" s="26" t="n">
         <v>0</v>
@@ -20815,7 +20855,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-cat-gyt-2026-08-02-cat).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4500 (atc-arg2-cjh-caa-2026-08-01-cjh).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -20856,32 +20896,32 @@
       </c>
       <c r="AP71" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AQ71" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AR71" s="24" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro (Salta)</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="AS71" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AT71" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AU71" s="24" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="AV71" s="24" t="n"/>
@@ -20934,7 +20974,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:43.831258Z</t>
+          <t>2026-08-02T15:46:30.754443Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -20944,13 +20984,13 @@
       </c>
       <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.45045</v>
       </c>
       <c r="BN71" s="28" t="n"/>
       <c r="BO71" s="28" t="n"/>
@@ -20980,27 +21020,31 @@
       <c r="CM71" s="24" t="n"/>
       <c r="CN71" s="24" t="n"/>
       <c r="CO71" s="24" t="n"/>
-      <c r="CP71" s="24" t="n"/>
+      <c r="CP71" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>f61ec0eaa3ed4ea1</t>
+          <t>c37f709786c4400e</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:00Z</t>
+          <t>2026-08-02T18:00Z</t>
         </is>
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>401844026</t>
+          <t>401844019</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
@@ -21010,12 +21054,12 @@
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
@@ -21035,13 +21079,13 @@
         </is>
       </c>
       <c r="L72" s="26" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="M72" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.7</v>
       </c>
       <c r="N72" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.37037</v>
       </c>
       <c r="O72" s="28" t="n">
         <v>0.456135</v>
@@ -21050,7 +21094,7 @@
         <v>0.2</v>
       </c>
       <c r="Q72" s="28" t="n">
-        <v>-0.053669</v>
+        <v>0.08576499999999999</v>
       </c>
       <c r="R72" s="26" t="n">
         <v>0</v>
@@ -21079,7 +21123,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-arg2-dma-abo-2026-08-02-dma).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3700 (atc-arg2-ste-casm-2026-08-02-ste).</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -21097,7 +21141,7 @@
       <c r="AJ72" s="31" t="n"/>
       <c r="AK72" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL72" s="26" t="n">
@@ -21105,47 +21149,47 @@
       </c>
       <c r="AM72" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN72" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO72" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP72" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="AQ72" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="AR72" s="24" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="AS72" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="AT72" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="AU72" s="24" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="AV72" s="24" t="n"/>
@@ -21198,7 +21242,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:44.367919Z</t>
+          <t>2026-08-02T15:46:31.355163Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21208,13 +21252,13 @@
       </c>
       <c r="BJ72" s="25" t="n"/>
       <c r="BK72" s="26" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="BL72" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.7</v>
       </c>
       <c r="BM72" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.37037</v>
       </c>
       <c r="BN72" s="28" t="n"/>
       <c r="BO72" s="28" t="n"/>
@@ -21244,27 +21288,31 @@
       <c r="CM72" s="24" t="n"/>
       <c r="CN72" s="24" t="n"/>
       <c r="CO72" s="24" t="n"/>
-      <c r="CP72" s="24" t="n"/>
+      <c r="CP72" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>5109ef785f354463</t>
+          <t>09f95882ac534e41</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:30Z</t>
+          <t>2026-08-02T18:30Z</t>
         </is>
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>401844014</t>
+          <t>401844012</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
@@ -21274,12 +21322,12 @@
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -21299,13 +21347,13 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.460829</v>
       </c>
       <c r="O73" s="28" t="n">
         <v>0.456135</v>
@@ -21314,7 +21362,7 @@
         <v>0.2</v>
       </c>
       <c r="Q73" s="28" t="n">
-        <v>0.06551</v>
+        <v>-0.004694</v>
       </c>
       <c r="R73" s="26" t="n">
         <v>0</v>
@@ -21343,7 +21391,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-arg2-cat-gyt-2026-08-02-cat).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -21361,7 +21409,7 @@
       <c r="AJ73" s="31" t="n"/>
       <c r="AK73" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL73" s="26" t="n">
@@ -21369,47 +21417,47 @@
       </c>
       <c r="AM73" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN73" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO73" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP73" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AQ73" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AR73" s="24" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro (Salta)</t>
         </is>
       </c>
       <c r="AS73" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="AT73" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="AU73" s="24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="AV73" s="24" t="n"/>
@@ -21462,7 +21510,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:44.924772Z</t>
+          <t>2026-08-02T15:46:31.317492Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21472,13 +21520,13 @@
       </c>
       <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.460829</v>
       </c>
       <c r="BN73" s="28" t="n"/>
       <c r="BO73" s="28" t="n"/>
@@ -21508,27 +21556,31 @@
       <c r="CM73" s="24" t="n"/>
       <c r="CN73" s="24" t="n"/>
       <c r="CO73" s="24" t="n"/>
-      <c r="CP73" s="24" t="n"/>
+      <c r="CP73" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>d38a7a67a080456e</t>
+          <t>326e981d1d6f435a</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T01:00Z</t>
+          <t>2026-08-02T19:00Z</t>
         </is>
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>401877966</t>
+          <t>401844026</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
@@ -21538,12 +21590,12 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -21563,13 +21615,13 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>2.17</v>
+        <v>1.961538</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.509804</v>
       </c>
       <c r="O74" s="28" t="n">
         <v>0.456135</v>
@@ -21578,7 +21630,7 @@
         <v>0.2</v>
       </c>
       <c r="Q74" s="28" t="n">
-        <v>-0.004694</v>
+        <v>-0.053669</v>
       </c>
       <c r="R74" s="26" t="n">
         <v>0</v>
@@ -21607,7 +21659,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lco-san-onc-2026-08-02-san).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-arg2-dma-abo-2026-08-02-dma).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -21648,32 +21700,32 @@
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -21726,7 +21778,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:45.478968Z</t>
+          <t>2026-08-02T15:46:31.887658Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -21736,13 +21788,13 @@
       </c>
       <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>117</v>
+        <v>-104</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>2.17</v>
+        <v>1.961538</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.509804</v>
       </c>
       <c r="BN74" s="28" t="n"/>
       <c r="BO74" s="28" t="n"/>
@@ -21772,27 +21824,31 @@
       <c r="CM74" s="24" t="n"/>
       <c r="CN74" s="24" t="n"/>
       <c r="CO74" s="24" t="n"/>
-      <c r="CP74" s="24" t="n"/>
+      <c r="CP74" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>8693acfb41e243fd</t>
+          <t>98881234852546be</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:00Z</t>
+          <t>2026-08-02T19:30Z</t>
         </is>
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>401850609</t>
+          <t>401844014</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
@@ -21802,12 +21858,12 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr">
@@ -21836,13 +21892,13 @@
         <v>0.4</v>
       </c>
       <c r="O75" s="28" t="n">
-        <v>0.5359159999999999</v>
+        <v>0.456135</v>
       </c>
       <c r="P75" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="Q75" s="28" t="n">
-        <v>0.135916</v>
+        <v>0.056135</v>
       </c>
       <c r="R75" s="26" t="n">
         <v>0</v>
@@ -21871,7 +21927,7 @@
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.4000 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4000 (atc-arg2-ccns-ala-2026-08-02-ccns).</t>
         </is>
       </c>
       <c r="AF75" s="31" t="inlineStr">
@@ -21912,32 +21968,32 @@
       </c>
       <c r="AP75" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="AQ75" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="AR75" s="24" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="AS75" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="AT75" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="AU75" s="24" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="AV75" s="24" t="n"/>
@@ -21990,7 +22046,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:46.605203Z</t>
+          <t>2026-08-02T15:46:32.444165Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -22036,27 +22092,31 @@
       <c r="CM75" s="24" t="n"/>
       <c r="CN75" s="24" t="n"/>
       <c r="CO75" s="24" t="n"/>
-      <c r="CP75" s="24" t="n"/>
+      <c r="CP75" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>fadf84ce72c64e10</t>
+          <t>f12e824945cc432f</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T21:30Z</t>
+          <t>2026-08-03T01:00Z</t>
         </is>
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>401850607</t>
+          <t>401877966</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
@@ -22066,12 +22126,12 @@
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
@@ -22091,22 +22151,22 @@
         </is>
       </c>
       <c r="L76" s="26" t="n">
-        <v>-170</v>
+        <v>117</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.17</v>
       </c>
       <c r="N76" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.460829</v>
       </c>
       <c r="O76" s="28" t="n">
-        <v>0.414794</v>
+        <v>0.456135</v>
       </c>
       <c r="P76" s="28" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="Q76" s="28" t="n">
-        <v>-0.214836</v>
+        <v>-0.004694</v>
       </c>
       <c r="R76" s="26" t="n">
         <v>0</v>
@@ -22135,7 +22195,7 @@
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6300 (atc-pdc-unc-hua-2026-08-02-unc).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4600 (atc-lco-san-onc-2026-08-02-san).</t>
         </is>
       </c>
       <c r="AF76" s="31" t="inlineStr">
@@ -22176,32 +22236,32 @@
       </c>
       <c r="AP76" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="AQ76" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="AR76" s="24" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="AS76" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="AT76" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="AU76" s="24" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Independiente Santa Fe</t>
         </is>
       </c>
       <c r="AV76" s="24" t="n"/>
@@ -22254,7 +22314,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:46.553813Z</t>
+          <t>2026-08-02T15:46:32.970430Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22264,13 +22324,13 @@
       </c>
       <c r="BJ76" s="25" t="n"/>
       <c r="BK76" s="26" t="n">
-        <v>-170</v>
+        <v>117</v>
       </c>
       <c r="BL76" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.17</v>
       </c>
       <c r="BM76" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.460829</v>
       </c>
       <c r="BN76" s="28" t="n"/>
       <c r="BO76" s="28" t="n"/>
@@ -22300,27 +22360,31 @@
       <c r="CM76" s="24" t="n"/>
       <c r="CN76" s="24" t="n"/>
       <c r="CO76" s="24" t="n"/>
-      <c r="CP76" s="24" t="n"/>
+      <c r="CP76" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>c263948c11c94638</t>
+          <t>f3602e6b0d094886</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:00Z</t>
+          <t>2026-08-02T19:00Z</t>
         </is>
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>401872734</t>
+          <t>401850609</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
@@ -22330,12 +22394,12 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G77" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr">
@@ -22355,13 +22419,13 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>-127</v>
+        <v>156</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.56</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.390625</v>
       </c>
       <c r="O77" s="28" t="n">
         <v>0.5359159999999999</v>
@@ -22370,10 +22434,10 @@
         <v>0.2</v>
       </c>
       <c r="Q77" s="28" t="n">
-        <v>-0.023555</v>
+        <v>0.145291</v>
       </c>
       <c r="R77" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S77" s="29" t="n">
         <v>1</v>
@@ -22399,7 +22463,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.5600 (atc-uru1-rcm-bri-2026-08-02-rcm).</t>
+          <t>Poisson-DC rates 1.84 (home) / 1.10 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-pdc-ser-ohi-2026-08-02-ser).</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -22417,7 +22481,7 @@
       <c r="AJ77" s="31" t="n"/>
       <c r="AK77" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL77" s="26" t="n">
@@ -22425,47 +22489,47 @@
       </c>
       <c r="AM77" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN77" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO77" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP77" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="AQ77" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="AR77" s="24" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="AS77" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="AT77" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="AU77" s="24" t="inlineStr">
         <is>
-          <t>Racing (Montevideo)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="AV77" s="24" t="n"/>
@@ -22518,7 +22582,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:47.678863Z</t>
+          <t>2026-08-02T15:46:34.034224Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22528,13 +22592,13 @@
       </c>
       <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
-        <v>-127</v>
+        <v>156</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.56</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.390625</v>
       </c>
       <c r="BN77" s="28" t="n"/>
       <c r="BO77" s="28" t="n"/>
@@ -22564,27 +22628,31 @@
       <c r="CM77" s="24" t="n"/>
       <c r="CN77" s="24" t="n"/>
       <c r="CO77" s="24" t="n"/>
-      <c r="CP77" s="24" t="n"/>
+      <c r="CP77" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>eb5c055fd013485c</t>
+          <t>48f179ce6d1b4410</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T20:30Z</t>
+          <t>2026-08-02T21:30Z</t>
         </is>
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>401859644</t>
+          <t>401850607</t>
         </is>
       </c>
       <c r="E78" s="24" t="inlineStr">
@@ -22594,12 +22662,12 @@
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G78" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr">
@@ -22619,22 +22687,22 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-186</v>
+        <v>-178</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.561798</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.640288</v>
       </c>
       <c r="O78" s="28" t="n">
-        <v>0.456135</v>
+        <v>0.414794</v>
       </c>
       <c r="P78" s="28" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q78" s="28" t="n">
-        <v>-0.194215</v>
+        <v>-0.225494</v>
       </c>
       <c r="R78" s="26" t="n">
         <v>0</v>
@@ -22663,7 +22731,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6500 (atc-ecu1-mac-gua-2026-08-02-mac).</t>
+          <t>Poisson-DC rates 1.41 (home) / 1.16 (away) from EWMA attack/defense strengths. Executable ask 0.6400 (atc-pdc-unc-hua-2026-08-02-unc).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -22704,32 +22772,32 @@
       </c>
       <c r="AP78" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="AQ78" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="AR78" s="24" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="AS78" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="AT78" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="AU78" s="24" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="AV78" s="24" t="n"/>
@@ -22782,7 +22850,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:48.243225Z</t>
+          <t>2026-08-02T15:46:33.999302Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -22792,13 +22860,13 @@
       </c>
       <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>-186</v>
+        <v>-178</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.561798</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.640288</v>
       </c>
       <c r="BN78" s="28" t="n"/>
       <c r="BO78" s="28" t="n"/>
@@ -22828,27 +22896,31 @@
       <c r="CM78" s="24" t="n"/>
       <c r="CN78" s="24" t="n"/>
       <c r="CO78" s="24" t="n"/>
-      <c r="CP78" s="24" t="n"/>
+      <c r="CP78" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>d0190a70cb46499d</t>
+          <t>3617d49c14bc4a29</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T23:10Z</t>
+          <t>2026-08-02T20:30Z</t>
         </is>
       </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
-          <t>401859718</t>
+          <t>401859644</t>
         </is>
       </c>
       <c r="E79" s="24" t="inlineStr">
@@ -22858,12 +22930,12 @@
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G79" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="H79" s="24" t="inlineStr">
@@ -22873,7 +22945,7 @@
       </c>
       <c r="I79" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J79" s="25" t="n"/>
@@ -22883,22 +22955,22 @@
         </is>
       </c>
       <c r="L79" s="26" t="n">
-        <v>203</v>
+        <v>-194</v>
       </c>
       <c r="M79" s="27" t="n">
-        <v>3.03</v>
+        <v>1.515464</v>
       </c>
       <c r="N79" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.659864</v>
       </c>
       <c r="O79" s="28" t="n">
-        <v>0.406677</v>
+        <v>0.456135</v>
       </c>
       <c r="P79" s="28" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="Q79" s="28" t="n">
-        <v>0.076644</v>
+        <v>-0.203729</v>
       </c>
       <c r="R79" s="26" t="n">
         <v>0</v>
@@ -22927,7 +22999,7 @@
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
+          <t>Poisson-DC rates 1.64 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.6600 (atc-ecu1-mac-gua-2026-08-02-mac).</t>
         </is>
       </c>
       <c r="AF79" s="31" t="inlineStr">
@@ -22945,7 +23017,7 @@
       <c r="AJ79" s="31" t="n"/>
       <c r="AK79" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL79" s="26" t="n">
@@ -22953,47 +23025,47 @@
       </c>
       <c r="AM79" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN79" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO79" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP79" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="AQ79" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="AR79" s="24" t="inlineStr">
         <is>
-          <t>Barcelona SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="AS79" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="AT79" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="AU79" s="24" t="inlineStr">
         <is>
-          <t>Leones</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="AV79" s="24" t="n"/>
@@ -23046,7 +23118,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:48.734342Z</t>
+          <t>2026-08-02T15:46:35.744825Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -23056,13 +23128,13 @@
       </c>
       <c r="BJ79" s="25" t="n"/>
       <c r="BK79" s="26" t="n">
-        <v>203</v>
+        <v>-194</v>
       </c>
       <c r="BL79" s="27" t="n">
-        <v>3.03</v>
+        <v>1.515464</v>
       </c>
       <c r="BM79" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.659864</v>
       </c>
       <c r="BN79" s="28" t="n"/>
       <c r="BO79" s="28" t="n"/>
@@ -23092,27 +23164,31 @@
       <c r="CM79" s="24" t="n"/>
       <c r="CN79" s="24" t="n"/>
       <c r="CO79" s="24" t="n"/>
-      <c r="CP79" s="24" t="n"/>
+      <c r="CP79" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>2d67de72f6ba48bd</t>
+          <t>4a8b4111f6084338</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T14:30Z</t>
+          <t>2026-08-02T23:10Z</t>
         </is>
       </c>
       <c r="D80" s="24" t="inlineStr">
         <is>
-          <t>401898711</t>
+          <t>401859718</t>
         </is>
       </c>
       <c r="E80" s="24" t="inlineStr">
@@ -23122,12 +23198,12 @@
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="G80" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="H80" s="24" t="inlineStr">
@@ -23137,7 +23213,7 @@
       </c>
       <c r="I80" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J80" s="25" t="n"/>
@@ -23147,22 +23223,22 @@
         </is>
       </c>
       <c r="L80" s="26" t="n">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="M80" s="27" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="N80" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.330033</v>
       </c>
       <c r="O80" s="28" t="n">
-        <v>0.395816</v>
+        <v>0.406677</v>
       </c>
       <c r="P80" s="28" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q80" s="28" t="n">
-        <v>0.005191</v>
+        <v>0.076644</v>
       </c>
       <c r="R80" s="26" t="n">
         <v>0</v>
@@ -23191,7 +23267,7 @@
       <c r="AD80" s="24" t="n"/>
       <c r="AE80" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-clbf-tra-udi-2026-08-02-tra).</t>
+          <t>Poisson-DC rates 1.38 (home) / 1.56 (away) from EWMA attack/defense strengths. Executable ask 0.3300 (atc-ecu1-leo-bsc-2026-08-02-bsc).</t>
         </is>
       </c>
       <c r="AF80" s="31" t="inlineStr">
@@ -23209,7 +23285,7 @@
       <c r="AJ80" s="31" t="n"/>
       <c r="AK80" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL80" s="26" t="n">
@@ -23217,47 +23293,47 @@
       </c>
       <c r="AM80" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN80" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO80" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP80" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="AQ80" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="AR80" s="24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona SC</t>
         </is>
       </c>
       <c r="AS80" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="AT80" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="AU80" s="24" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Leones</t>
         </is>
       </c>
       <c r="AV80" s="24" t="n"/>
@@ -23310,7 +23386,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:50.866524Z</t>
+          <t>2026-08-02T15:46:36.285171Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -23320,13 +23396,13 @@
       </c>
       <c r="BJ80" s="25" t="n"/>
       <c r="BK80" s="26" t="n">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="BL80" s="27" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="BM80" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.330033</v>
       </c>
       <c r="BN80" s="28" t="n"/>
       <c r="BO80" s="28" t="n"/>
@@ -23356,17 +23432,21 @@
       <c r="CM80" s="24" t="n"/>
       <c r="CN80" s="24" t="n"/>
       <c r="CO80" s="24" t="n"/>
-      <c r="CP80" s="24" t="n"/>
+      <c r="CP80" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>c75bdecc61de4110</t>
+          <t>c03585b82e134879</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -23411,13 +23491,13 @@
         </is>
       </c>
       <c r="L81" s="26" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="M81" s="27" t="n">
-        <v>2.08</v>
+        <v>1.961538</v>
       </c>
       <c r="N81" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.509804</v>
       </c>
       <c r="O81" s="28" t="n">
         <v>0.395592</v>
@@ -23426,7 +23506,7 @@
         <v>0.04</v>
       </c>
       <c r="Q81" s="28" t="n">
-        <v>-0.085177</v>
+        <v>-0.114212</v>
       </c>
       <c r="R81" s="26" t="n">
         <v>0</v>
@@ -23455,7 +23535,7 @@
       <c r="AD81" s="24" t="n"/>
       <c r="AE81" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.40 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.4800 (atc-clbf-sun-wre-2026-08-02-sun).</t>
+          <t>Poisson-DC rates 1.40 (home) / 1.24 (away) from EWMA attack/defense strengths. Executable ask 0.5100 (atc-clbf-sun-wre-2026-08-02-sun).</t>
         </is>
       </c>
       <c r="AF81" s="31" t="inlineStr">
@@ -23574,7 +23654,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:50.974234Z</t>
+          <t>2026-08-02T15:46:37.855949Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -23584,13 +23664,13 @@
       </c>
       <c r="BJ81" s="25" t="n"/>
       <c r="BK81" s="26" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="BL81" s="27" t="n">
-        <v>2.08</v>
+        <v>1.961538</v>
       </c>
       <c r="BM81" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.509804</v>
       </c>
       <c r="BN81" s="28" t="n"/>
       <c r="BO81" s="28" t="n"/>
@@ -23620,17 +23700,21 @@
       <c r="CM81" s="24" t="n"/>
       <c r="CN81" s="24" t="n"/>
       <c r="CO81" s="24" t="n"/>
-      <c r="CP81" s="24" t="n"/>
+      <c r="CP81" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>84b998c94a984f6b</t>
+          <t>812c02c893834725</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:47.245126Z</t>
+          <t>2026-08-02T15:49:40.829108Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -23838,7 +23922,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:02:51.442026Z</t>
+          <t>2026-08-02T15:46:38.357498Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
@@ -23884,7 +23968,11 @@
       <c r="CM82" s="24" t="n"/>
       <c r="CN82" s="24" t="n"/>
       <c r="CO82" s="24" t="n"/>
-      <c r="CP82" s="24" t="n"/>
+      <c r="CP82" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/soccer.xlsx
+++ b/data/research/soccer.xlsx
@@ -15660,18 +15660,32 @@
       </c>
       <c r="U52" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y52" s="25" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
+      <c r="AC52" s="30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:39:53.616358Z</t>
+        </is>
+      </c>
       <c r="AE52" s="31" t="inlineStr">
         <is>
           <t>Poisson-DC rates 1.26 (home) / 1.06 (away) from EWMA attack/defense strengths. Executable ask 0.3900 (atc-clbf-tra-udi-2026-08-02-tra).</t>
@@ -20299,12 +20313,12 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>65e3b4f475a748df</t>
+          <t>70aef8c352cf40f1</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -20512,7 +20526,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:08.431356Z</t>
+          <t>2026-08-02T16:47:34.772770Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20568,12 +20582,12 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>b245873e9e554042</t>
+          <t>515f74ba1e2e4ddf</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -20618,13 +20632,13 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="M70" s="27" t="n">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.229885</v>
+        <v>0.21978</v>
       </c>
       <c r="O70" s="28" t="n">
         <v>0.398039</v>
@@ -20633,10 +20647,10 @@
         <v>0.2</v>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>0.168154</v>
+        <v>0.178259</v>
       </c>
       <c r="R70" s="26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="S70" s="29" t="n">
         <v>1</v>
@@ -20662,7 +20676,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2300 (atc-lpa-new-boc-2026-08-02-new).</t>
+          <t>Poisson-DC rates 1.46 (home) / 1.30 (away) from EWMA attack/defense strengths. Executable ask 0.2200 (atc-lpa-new-boc-2026-08-02-new).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -20781,7 +20795,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:08.536425Z</t>
+          <t>2026-08-02T16:47:34.761524Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -20791,13 +20805,13 @@
       </c>
       <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="BL70" s="27" t="n">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.229885</v>
+        <v>0.21978</v>
       </c>
       <c r="BN70" s="28" t="n"/>
       <c r="BO70" s="28" t="n"/>
@@ -20837,12 +20851,12 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>079e03c7ad3f4597</t>
+          <t>dabc34675953450d</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -21050,7 +21064,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:08.980617Z</t>
+          <t>2026-08-02T16:47:35.319407Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -21106,12 +21120,12 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>60c11542f9d14dcb</t>
+          <t>3dc37e7e9ec74a59</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -21319,7 +21333,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:09.690642Z</t>
+          <t>2026-08-02T16:47:35.929520Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21375,12 +21389,12 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>fef45de45c904f50</t>
+          <t>97ba1cb700cb43c7</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -21588,7 +21602,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:10.319650Z</t>
+          <t>2026-08-02T16:47:36.485049Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21644,12 +21658,12 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>06cb55ce4b104aa8</t>
+          <t>95be0e3f07f44fd6</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -21857,7 +21871,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:10.262963Z</t>
+          <t>2026-08-02T16:47:36.452468Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -21913,12 +21927,12 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>46b66e5bd4974ad2</t>
+          <t>401da7c23348410f</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -22126,7 +22140,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:10.820622Z</t>
+          <t>2026-08-02T16:47:36.997419Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -22182,12 +22196,12 @@
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>5837966c80e343ae</t>
+          <t>413ff14b66294566</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -22395,7 +22409,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:11.344005Z</t>
+          <t>2026-08-02T16:47:37.549387Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22451,12 +22465,12 @@
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>a6eb7d6b34f444b0</t>
+          <t>32ba51c067c54435</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
@@ -22664,7 +22678,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:11.996978Z</t>
+          <t>2026-08-02T16:47:38.138409Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22720,12 +22734,12 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>b380f2df213e4b4b</t>
+          <t>6725a42eadf9435f</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -22933,7 +22947,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:13.051822Z</t>
+          <t>2026-08-02T16:47:39.241482Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -22989,12 +23003,12 @@
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>3d91d425059841ea</t>
+          <t>b6c4cf177dcf4672</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
@@ -23202,7 +23216,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:13.076403Z</t>
+          <t>2026-08-02T16:47:39.244934Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -23258,12 +23272,12 @@
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="24" t="inlineStr">
         <is>
-          <t>ad9cbe9b7e93465a</t>
+          <t>6998db29de93467c</t>
         </is>
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -23471,7 +23485,7 @@
       </c>
       <c r="BH80" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:14.638862Z</t>
+          <t>2026-08-02T16:47:40.806031Z</t>
         </is>
       </c>
       <c r="BI80" s="24" t="inlineStr">
@@ -23527,12 +23541,12 @@
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>68744155690146ed</t>
+          <t>e0b3223862d443e5</t>
         </is>
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -23740,7 +23754,7 @@
       </c>
       <c r="BH81" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:15.198916Z</t>
+          <t>2026-08-02T16:47:41.338397Z</t>
         </is>
       </c>
       <c r="BI81" s="24" t="inlineStr">
@@ -23796,12 +23810,12 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>a4f7fe9a35d54329</t>
+          <t>7e0a28d64c9f45db</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:13:18.780884Z</t>
+          <t>2026-08-02T16:51:15.727312Z</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -24009,7 +24023,7 @@
       </c>
       <c r="BH82" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:10:17.255205Z</t>
+          <t>2026-08-02T16:47:43.017604Z</t>
         </is>
       </c>
       <c r="BI82" s="24" t="inlineStr">
